--- a/predictions/model_compare.xlsx
+++ b/predictions/model_compare.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ripa_\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ripa_\Desktop\Programing\IndyCar_Project\predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F23E69E-BB1C-4D19-8F4C-0B9BBDE10D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2B043F-FAC7-4114-98E9-A1461423C0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" firstSheet="2" activeTab="2" xr2:uid="{74EB7EE7-EB5C-4423-87E4-FE46F1C4926A}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{74EB7EE7-EB5C-4423-87E4-FE46F1C4926A}"/>
   </bookViews>
   <sheets>
     <sheet name="Pre-Qualy" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="87">
   <si>
     <t>Model</t>
   </si>
@@ -406,6 +406,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -417,10 +421,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -943,22 +943,22 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9"/>
+      <c r="I1" s="11"/>
       <c r="J1" t="s">
         <v>51</v>
       </c>
@@ -1197,22 +1197,22 @@
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="8" t="s">
+      <c r="C11" s="13"/>
+      <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9" t="s">
+      <c r="E11" s="10"/>
+      <c r="F11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
+      <c r="G11" s="11"/>
+      <c r="H11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="9"/>
+      <c r="I11" s="11"/>
       <c r="J11" t="s">
         <v>50</v>
       </c>
@@ -1677,22 +1677,22 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1"/>
@@ -2291,10 +2291,6 @@
       </c>
       <c r="D24">
         <v>0.24890000000000001</v>
-      </c>
-      <c r="F24">
-        <f>C24*25</f>
-        <v>5.2025000000000006</v>
       </c>
     </row>
   </sheetData>
@@ -6434,7 +6430,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="17.20703125" bestFit="1" customWidth="1"/>
@@ -6494,15 +6490,15 @@
       <c r="A2" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="9">
         <v>6.23</v>
       </c>
       <c r="C2" s="5">
-        <f>B2-L2</f>
+        <f t="shared" ref="C2:C33" si="0">B2-L2</f>
         <v>1.0300000000000002</v>
       </c>
       <c r="D2" s="5">
-        <f>B2+L2</f>
+        <f t="shared" ref="D2:D33" si="1">B2+L2</f>
         <v>11.43</v>
       </c>
       <c r="E2" s="5">
@@ -6535,15 +6531,15 @@
       <c r="A3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="9">
         <v>7.33</v>
       </c>
       <c r="C3" s="5">
-        <f>B3-L3</f>
+        <f t="shared" si="0"/>
         <v>2.13</v>
       </c>
       <c r="D3" s="5">
-        <f>B3+L3</f>
+        <f t="shared" si="1"/>
         <v>12.530000000000001</v>
       </c>
       <c r="E3" s="5">
@@ -6576,15 +6572,15 @@
       <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="9">
         <v>8.7899999999999991</v>
       </c>
       <c r="C4" s="5">
-        <f>B4-L4</f>
+        <f t="shared" si="0"/>
         <v>3.589999999999999</v>
       </c>
       <c r="D4" s="5">
-        <f>B4+L4</f>
+        <f t="shared" si="1"/>
         <v>13.989999999999998</v>
       </c>
       <c r="E4" s="5">
@@ -6617,15 +6613,15 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="9">
         <v>8.8000000000000007</v>
       </c>
       <c r="C5" s="5">
-        <f>B5-L5</f>
+        <f t="shared" si="0"/>
         <v>3.6000000000000005</v>
       </c>
       <c r="D5" s="5">
-        <f>B5+L5</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E5" s="5">
@@ -6658,15 +6654,15 @@
       <c r="A6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="9">
         <v>8.85</v>
       </c>
       <c r="C6" s="5">
-        <f>B6-L6</f>
+        <f t="shared" si="0"/>
         <v>3.6499999999999995</v>
       </c>
       <c r="D6" s="5">
-        <f>B6+L6</f>
+        <f t="shared" si="1"/>
         <v>14.05</v>
       </c>
       <c r="E6" s="5">
@@ -6699,15 +6695,15 @@
       <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="9">
         <v>9.3000000000000007</v>
       </c>
       <c r="C7" s="5">
-        <f>B7-L7</f>
+        <f t="shared" si="0"/>
         <v>4.1000000000000005</v>
       </c>
       <c r="D7" s="5">
-        <f>B7+L7</f>
+        <f t="shared" si="1"/>
         <v>14.5</v>
       </c>
       <c r="E7" s="5">
@@ -6740,15 +6736,15 @@
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="9">
         <v>9.57</v>
       </c>
       <c r="C8" s="5">
-        <f>B8-L8</f>
+        <f t="shared" si="0"/>
         <v>4.37</v>
       </c>
       <c r="D8" s="5">
-        <f>B8+L8</f>
+        <f t="shared" si="1"/>
         <v>14.77</v>
       </c>
       <c r="E8" s="5">
@@ -6781,15 +6777,15 @@
       <c r="A9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="9">
         <v>10.210000000000001</v>
       </c>
       <c r="C9" s="5">
-        <f>B9-L9</f>
+        <f t="shared" si="0"/>
         <v>5.0100000000000007</v>
       </c>
       <c r="D9" s="5">
-        <f>B9+L9</f>
+        <f t="shared" si="1"/>
         <v>15.41</v>
       </c>
       <c r="E9" s="5">
@@ -6822,15 +6818,15 @@
       <c r="A10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="9">
         <v>10.56</v>
       </c>
       <c r="C10" s="5">
-        <f>B10-L10</f>
+        <f t="shared" si="0"/>
         <v>5.36</v>
       </c>
       <c r="D10" s="5">
-        <f>B10+L10</f>
+        <f t="shared" si="1"/>
         <v>15.760000000000002</v>
       </c>
       <c r="E10" s="5">
@@ -6863,15 +6859,15 @@
       <c r="A11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="9">
         <v>10.63</v>
       </c>
       <c r="C11" s="5">
-        <f>B11-L11</f>
+        <f t="shared" si="0"/>
         <v>5.4300000000000006</v>
       </c>
       <c r="D11" s="5">
-        <f>B11+L11</f>
+        <f t="shared" si="1"/>
         <v>15.830000000000002</v>
       </c>
       <c r="E11" s="5">
@@ -6904,15 +6900,15 @@
       <c r="A12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="9">
         <v>10.91</v>
       </c>
       <c r="C12" s="5">
-        <f>B12-L12</f>
+        <f t="shared" si="0"/>
         <v>5.71</v>
       </c>
       <c r="D12" s="5">
-        <f>B12+L12</f>
+        <f t="shared" si="1"/>
         <v>16.11</v>
       </c>
       <c r="E12" s="5">
@@ -6945,15 +6941,15 @@
       <c r="A13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="9">
         <v>10.95</v>
       </c>
       <c r="C13" s="5">
-        <f>B13-L13</f>
+        <f t="shared" si="0"/>
         <v>5.7499999999999991</v>
       </c>
       <c r="D13" s="5">
-        <f>B13+L13</f>
+        <f t="shared" si="1"/>
         <v>16.149999999999999</v>
       </c>
       <c r="E13" s="5">
@@ -6986,15 +6982,15 @@
       <c r="A14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="9">
         <v>11.51</v>
       </c>
       <c r="C14" s="5">
-        <f>B14-L14</f>
+        <f t="shared" si="0"/>
         <v>6.31</v>
       </c>
       <c r="D14" s="5">
-        <f>B14+L14</f>
+        <f t="shared" si="1"/>
         <v>16.71</v>
       </c>
       <c r="E14" s="5">
@@ -7027,15 +7023,15 @@
       <c r="A15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="9">
         <v>11.97</v>
       </c>
       <c r="C15" s="5">
-        <f>B15-L15</f>
+        <f t="shared" si="0"/>
         <v>6.7700000000000005</v>
       </c>
       <c r="D15" s="5">
-        <f>B15+L15</f>
+        <f t="shared" si="1"/>
         <v>17.170000000000002</v>
       </c>
       <c r="E15" s="5">
@@ -7068,15 +7064,15 @@
       <c r="A16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="9">
         <v>12.74</v>
       </c>
       <c r="C16" s="5">
-        <f>B16-L16</f>
+        <f t="shared" si="0"/>
         <v>7.54</v>
       </c>
       <c r="D16" s="5">
-        <f>B16+L16</f>
+        <f t="shared" si="1"/>
         <v>17.940000000000001</v>
       </c>
       <c r="E16" s="5">
@@ -7109,15 +7105,15 @@
       <c r="A17" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="9">
         <v>12.75</v>
       </c>
       <c r="C17" s="5">
-        <f>B17-L17</f>
+        <f t="shared" si="0"/>
         <v>7.55</v>
       </c>
       <c r="D17" s="5">
-        <f>B17+L17</f>
+        <f t="shared" si="1"/>
         <v>17.95</v>
       </c>
       <c r="E17" s="5">
@@ -7150,15 +7146,15 @@
       <c r="A18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="9">
         <v>12.94</v>
       </c>
       <c r="C18" s="5">
-        <f>B18-L18</f>
+        <f t="shared" si="0"/>
         <v>7.7399999999999993</v>
       </c>
       <c r="D18" s="5">
-        <f>B18+L18</f>
+        <f t="shared" si="1"/>
         <v>18.14</v>
       </c>
       <c r="E18" s="5">
@@ -7191,15 +7187,15 @@
       <c r="A19" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="9">
         <v>13.76</v>
       </c>
       <c r="C19" s="5">
-        <f>B19-L19</f>
+        <f t="shared" si="0"/>
         <v>8.5599999999999987</v>
       </c>
       <c r="D19" s="5">
-        <f>B19+L19</f>
+        <f t="shared" si="1"/>
         <v>18.96</v>
       </c>
       <c r="E19" s="5">
@@ -7232,15 +7228,15 @@
       <c r="A20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="9">
         <v>14.13</v>
       </c>
       <c r="C20" s="5">
-        <f>B20-L20</f>
+        <f t="shared" si="0"/>
         <v>8.93</v>
       </c>
       <c r="D20" s="5">
-        <f>B20+L20</f>
+        <f t="shared" si="1"/>
         <v>19.330000000000002</v>
       </c>
       <c r="E20" s="5">
@@ -7273,15 +7269,15 @@
       <c r="A21" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="9">
         <v>14.49</v>
       </c>
       <c r="C21" s="5">
-        <f>B21-L21</f>
+        <f t="shared" si="0"/>
         <v>9.2899999999999991</v>
       </c>
       <c r="D21" s="5">
-        <f>B21+L21</f>
+        <f t="shared" si="1"/>
         <v>19.690000000000001</v>
       </c>
       <c r="E21" s="5">
@@ -7314,15 +7310,15 @@
       <c r="A22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="9">
         <v>14.54</v>
       </c>
       <c r="C22" s="5">
-        <f>B22-L22</f>
+        <f t="shared" si="0"/>
         <v>9.34</v>
       </c>
       <c r="D22" s="5">
-        <f>B22+L22</f>
+        <f t="shared" si="1"/>
         <v>19.739999999999998</v>
       </c>
       <c r="E22" s="5">
@@ -7355,15 +7351,15 @@
       <c r="A23" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="9">
         <v>15.99</v>
       </c>
       <c r="C23" s="5">
-        <f>B23-L23</f>
+        <f t="shared" si="0"/>
         <v>10.79</v>
       </c>
       <c r="D23" s="5">
-        <f>B23+L23</f>
+        <f t="shared" si="1"/>
         <v>21.19</v>
       </c>
       <c r="E23" s="5">
@@ -7396,15 +7392,15 @@
       <c r="A24" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="9">
         <v>16.36</v>
       </c>
       <c r="C24" s="5">
-        <f>B24-L24</f>
+        <f t="shared" si="0"/>
         <v>11.16</v>
       </c>
       <c r="D24" s="5">
-        <f>B24+L24</f>
+        <f t="shared" si="1"/>
         <v>21.56</v>
       </c>
       <c r="E24" s="5">
@@ -7437,15 +7433,15 @@
       <c r="A25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="9">
         <v>17.11</v>
       </c>
       <c r="C25" s="5">
-        <f>B25-L25</f>
+        <f t="shared" si="0"/>
         <v>11.91</v>
       </c>
       <c r="D25" s="5">
-        <f>B25+L25</f>
+        <f t="shared" si="1"/>
         <v>22.31</v>
       </c>
       <c r="E25" s="5">
@@ -7478,15 +7474,15 @@
       <c r="A26" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="9">
         <v>17.440000000000001</v>
       </c>
       <c r="C26" s="5">
-        <f>B26-L26</f>
+        <f t="shared" si="0"/>
         <v>12.240000000000002</v>
       </c>
       <c r="D26" s="5">
-        <f>B26+L26</f>
+        <f t="shared" si="1"/>
         <v>22.64</v>
       </c>
       <c r="E26" s="5">
@@ -7523,11 +7519,11 @@
         <v>8.4700000000000006</v>
       </c>
       <c r="C27" s="5">
-        <f>B27-L27</f>
+        <f t="shared" si="0"/>
         <v>3.1000000000000005</v>
       </c>
       <c r="D27" s="5">
-        <f>B27+L27</f>
+        <f t="shared" si="1"/>
         <v>13.84</v>
       </c>
       <c r="E27" s="5">
@@ -7536,10 +7532,10 @@
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="8">
         <v>10</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="8">
         <v>24</v>
       </c>
       <c r="I27" t="s">
@@ -7565,11 +7561,11 @@
         <v>8.59</v>
       </c>
       <c r="C28" s="5">
-        <f>B28-L28</f>
+        <f t="shared" si="0"/>
         <v>3.2199999999999998</v>
       </c>
       <c r="D28" s="5">
-        <f>B28+L28</f>
+        <f t="shared" si="1"/>
         <v>13.96</v>
       </c>
       <c r="E28" s="5">
@@ -7578,10 +7574,10 @@
       <c r="F28">
         <v>2</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="8">
         <v>1</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="8">
         <v>8</v>
       </c>
       <c r="I28" t="s">
@@ -7608,11 +7604,11 @@
         <v>9.01</v>
       </c>
       <c r="C29" s="5">
-        <f>B29-L29</f>
+        <f t="shared" si="0"/>
         <v>3.6399999999999997</v>
       </c>
       <c r="D29" s="5">
-        <f>B29+L29</f>
+        <f t="shared" si="1"/>
         <v>14.379999999999999</v>
       </c>
       <c r="E29" s="5">
@@ -7621,10 +7617,10 @@
       <c r="F29">
         <v>3</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="8">
         <v>2</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="8">
         <v>4</v>
       </c>
       <c r="I29" t="s">
@@ -7646,15 +7642,15 @@
       <c r="A30" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="9">
         <v>9.36</v>
       </c>
       <c r="C30" s="5">
-        <f>B30-L30</f>
+        <f t="shared" si="0"/>
         <v>3.9899999999999993</v>
       </c>
       <c r="D30" s="5">
-        <f>B30+L30</f>
+        <f t="shared" si="1"/>
         <v>14.73</v>
       </c>
       <c r="E30" s="5">
@@ -7663,10 +7659,10 @@
       <c r="F30">
         <v>4</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="8">
         <v>3</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="8">
         <v>1</v>
       </c>
       <c r="I30" t="s">
@@ -7688,15 +7684,15 @@
       <c r="A31" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="9">
         <v>9.6999999999999993</v>
       </c>
       <c r="C31" s="5">
-        <f>B31-L31</f>
+        <f t="shared" si="0"/>
         <v>4.3299999999999992</v>
       </c>
       <c r="D31" s="5">
-        <f>B31+L31</f>
+        <f t="shared" si="1"/>
         <v>15.07</v>
       </c>
       <c r="E31" s="5">
@@ -7705,10 +7701,10 @@
       <c r="F31">
         <v>5</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="8">
         <v>4</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="8">
         <v>9</v>
       </c>
       <c r="I31" t="s">
@@ -7734,11 +7730,11 @@
         <v>9.92</v>
       </c>
       <c r="C32" s="5">
-        <f>B32-L32</f>
+        <f t="shared" si="0"/>
         <v>4.55</v>
       </c>
       <c r="D32" s="5">
-        <f>B32+L32</f>
+        <f t="shared" si="1"/>
         <v>15.29</v>
       </c>
       <c r="E32" s="5">
@@ -7747,10 +7743,10 @@
       <c r="F32">
         <v>6</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="8">
         <v>5</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="8">
         <v>7</v>
       </c>
       <c r="I32" t="s">
@@ -7776,11 +7772,11 @@
         <v>10.199999999999999</v>
       </c>
       <c r="C33" s="5">
-        <f>B33-L33</f>
+        <f t="shared" si="0"/>
         <v>4.8299999999999992</v>
       </c>
       <c r="D33" s="5">
-        <f>B33+L33</f>
+        <f t="shared" si="1"/>
         <v>15.57</v>
       </c>
       <c r="E33" s="5">
@@ -7789,10 +7785,10 @@
       <c r="F33">
         <v>7</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="8">
         <v>18</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="8">
         <v>18</v>
       </c>
       <c r="I33" t="s">
@@ -7818,11 +7814,11 @@
         <v>10.42</v>
       </c>
       <c r="C34" s="5">
-        <f>B34-L34</f>
+        <f t="shared" ref="C34:C65" si="2">B34-L34</f>
         <v>5.05</v>
       </c>
       <c r="D34" s="5">
-        <f>B34+L34</f>
+        <f t="shared" ref="D34:D65" si="3">B34+L34</f>
         <v>15.79</v>
       </c>
       <c r="E34" s="5">
@@ -7831,10 +7827,10 @@
       <c r="F34">
         <v>8</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="8">
         <v>6</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="8">
         <v>2</v>
       </c>
       <c r="I34" t="s">
@@ -7856,15 +7852,15 @@
       <c r="A35" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="9">
         <v>10.57</v>
       </c>
       <c r="C35" s="5">
-        <f>B35-L35</f>
+        <f t="shared" si="2"/>
         <v>5.2</v>
       </c>
       <c r="D35" s="5">
-        <f>B35+L35</f>
+        <f t="shared" si="3"/>
         <v>15.940000000000001</v>
       </c>
       <c r="E35" s="5">
@@ -7873,10 +7869,10 @@
       <c r="F35">
         <v>9</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="8">
         <v>7</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="8">
         <v>3</v>
       </c>
       <c r="I35" t="s">
@@ -7902,11 +7898,11 @@
         <v>10.92</v>
       </c>
       <c r="C36" s="5">
-        <f>B36-L36</f>
+        <f t="shared" si="2"/>
         <v>5.55</v>
       </c>
       <c r="D36" s="5">
-        <f>B36+L36</f>
+        <f t="shared" si="3"/>
         <v>16.29</v>
       </c>
       <c r="E36" s="5">
@@ -7915,10 +7911,10 @@
       <c r="F36">
         <v>10</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="8">
         <v>8</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="8">
         <v>6</v>
       </c>
       <c r="I36" t="s">
@@ -7944,11 +7940,11 @@
         <v>11.64</v>
       </c>
       <c r="C37" s="5">
-        <f>B37-L37</f>
+        <f t="shared" si="2"/>
         <v>6.2700000000000005</v>
       </c>
       <c r="D37" s="5">
-        <f>B37+L37</f>
+        <f t="shared" si="3"/>
         <v>17.010000000000002</v>
       </c>
       <c r="E37" s="5">
@@ -7957,10 +7953,10 @@
       <c r="F37">
         <v>11</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="8">
         <v>19</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="8">
         <v>17</v>
       </c>
       <c r="I37" t="s">
@@ -7986,11 +7982,11 @@
         <v>11.74</v>
       </c>
       <c r="C38" s="5">
-        <f>B38-L38</f>
+        <f t="shared" si="2"/>
         <v>6.37</v>
       </c>
       <c r="D38" s="5">
-        <f>B38+L38</f>
+        <f t="shared" si="3"/>
         <v>17.11</v>
       </c>
       <c r="E38" s="5">
@@ -7999,10 +7995,10 @@
       <c r="F38">
         <v>12</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="8">
         <v>12</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="8">
         <v>16</v>
       </c>
       <c r="I38" t="s">
@@ -8028,11 +8024,11 @@
         <v>11.91</v>
       </c>
       <c r="C39" s="5">
-        <f>B39-L39</f>
+        <f t="shared" si="2"/>
         <v>6.54</v>
       </c>
       <c r="D39" s="5">
-        <f>B39+L39</f>
+        <f t="shared" si="3"/>
         <v>17.28</v>
       </c>
       <c r="E39" s="5">
@@ -8041,10 +8037,10 @@
       <c r="F39">
         <v>13</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="8">
         <v>13</v>
       </c>
-      <c r="H39" s="12">
+      <c r="H39" s="8">
         <v>22</v>
       </c>
       <c r="I39" t="s">
@@ -8070,11 +8066,11 @@
         <v>12.23</v>
       </c>
       <c r="C40" s="5">
-        <f>B40-L40</f>
+        <f t="shared" si="2"/>
         <v>6.86</v>
       </c>
       <c r="D40" s="5">
-        <f>B40+L40</f>
+        <f t="shared" si="3"/>
         <v>17.600000000000001</v>
       </c>
       <c r="E40" s="5">
@@ -8083,10 +8079,10 @@
       <c r="F40">
         <v>14</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G40" s="8">
         <v>20</v>
       </c>
-      <c r="H40" s="12">
+      <c r="H40" s="8">
         <v>13</v>
       </c>
       <c r="I40" t="s">
@@ -8112,11 +8108,11 @@
         <v>12.83</v>
       </c>
       <c r="C41" s="5">
-        <f>B41-L41</f>
+        <f t="shared" si="2"/>
         <v>7.46</v>
       </c>
       <c r="D41" s="5">
-        <f>B41+L41</f>
+        <f t="shared" si="3"/>
         <v>18.2</v>
       </c>
       <c r="E41" s="5">
@@ -8125,10 +8121,10 @@
       <c r="F41">
         <v>15</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="8">
         <v>9</v>
       </c>
-      <c r="H41" s="12">
+      <c r="H41" s="8">
         <v>5</v>
       </c>
       <c r="I41" t="s">
@@ -8154,11 +8150,11 @@
         <v>13.29</v>
       </c>
       <c r="C42" s="5">
-        <f>B42-L42</f>
+        <f t="shared" si="2"/>
         <v>7.919999999999999</v>
       </c>
       <c r="D42" s="5">
-        <f>B42+L42</f>
+        <f t="shared" si="3"/>
         <v>18.66</v>
       </c>
       <c r="E42" s="5">
@@ -8167,10 +8163,10 @@
       <c r="F42">
         <v>16</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="8">
         <v>21</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="8">
         <v>20</v>
       </c>
       <c r="I42" t="s">
@@ -8196,11 +8192,11 @@
         <v>13.91</v>
       </c>
       <c r="C43" s="5">
-        <f>B43-L43</f>
+        <f t="shared" si="2"/>
         <v>8.5399999999999991</v>
       </c>
       <c r="D43" s="5">
-        <f>B43+L43</f>
+        <f t="shared" si="3"/>
         <v>19.28</v>
       </c>
       <c r="E43" s="5">
@@ -8209,10 +8205,10 @@
       <c r="F43">
         <v>17</v>
       </c>
-      <c r="G43" s="12">
+      <c r="G43" s="8">
         <v>14</v>
       </c>
-      <c r="H43" s="12">
+      <c r="H43" s="8">
         <v>12</v>
       </c>
       <c r="I43" t="s">
@@ -8238,11 +8234,11 @@
         <v>14.26</v>
       </c>
       <c r="C44" s="5">
-        <f>B44-L44</f>
+        <f t="shared" si="2"/>
         <v>8.89</v>
       </c>
       <c r="D44" s="5">
-        <f>B44+L44</f>
+        <f t="shared" si="3"/>
         <v>19.63</v>
       </c>
       <c r="E44" s="5">
@@ -8251,10 +8247,10 @@
       <c r="F44">
         <v>18</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="8">
         <v>15</v>
       </c>
-      <c r="H44" s="12">
+      <c r="H44" s="8">
         <v>11</v>
       </c>
       <c r="I44" t="s">
@@ -8280,11 +8276,11 @@
         <v>14.5</v>
       </c>
       <c r="C45" s="5">
-        <f>B45-L45</f>
+        <f t="shared" si="2"/>
         <v>9.129999999999999</v>
       </c>
       <c r="D45" s="5">
-        <f>B45+L45</f>
+        <f t="shared" si="3"/>
         <v>19.87</v>
       </c>
       <c r="E45" s="5">
@@ -8293,10 +8289,10 @@
       <c r="F45">
         <v>19</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="8">
         <v>22</v>
       </c>
-      <c r="H45" s="12">
+      <c r="H45" s="8">
         <v>15</v>
       </c>
       <c r="I45" t="s">
@@ -8322,11 +8318,11 @@
         <v>14.76</v>
       </c>
       <c r="C46" s="5">
-        <f>B46-L46</f>
+        <f t="shared" si="2"/>
         <v>9.39</v>
       </c>
       <c r="D46" s="5">
-        <f>B46+L46</f>
+        <f t="shared" si="3"/>
         <v>20.13</v>
       </c>
       <c r="E46" s="5">
@@ -8335,10 +8331,10 @@
       <c r="F46">
         <v>20</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="8">
         <v>13</v>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="8">
         <v>19</v>
       </c>
       <c r="I46" t="s">
@@ -8364,11 +8360,11 @@
         <v>14.91</v>
       </c>
       <c r="C47" s="5">
-        <f>B47-L47</f>
+        <f t="shared" si="2"/>
         <v>9.5399999999999991</v>
       </c>
       <c r="D47" s="5">
-        <f>B47+L47</f>
+        <f t="shared" si="3"/>
         <v>20.28</v>
       </c>
       <c r="E47" s="5">
@@ -8377,10 +8373,10 @@
       <c r="F47">
         <v>21</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="8">
         <v>16</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="8">
         <v>25</v>
       </c>
       <c r="I47" t="s">
@@ -8406,11 +8402,11 @@
         <v>14.93</v>
       </c>
       <c r="C48" s="5">
-        <f>B48-L48</f>
+        <f t="shared" si="2"/>
         <v>9.5599999999999987</v>
       </c>
       <c r="D48" s="5">
-        <f>B48+L48</f>
+        <f t="shared" si="3"/>
         <v>20.3</v>
       </c>
       <c r="E48" s="5">
@@ -8419,10 +8415,10 @@
       <c r="F48">
         <v>22</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="8">
         <v>24</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="8">
         <v>21</v>
       </c>
       <c r="I48" t="s">
@@ -8448,11 +8444,11 @@
         <v>14.99</v>
       </c>
       <c r="C49" s="5">
-        <f>B49-L49</f>
+        <f t="shared" si="2"/>
         <v>9.620000000000001</v>
       </c>
       <c r="D49" s="5">
-        <f>B49+L49</f>
+        <f t="shared" si="3"/>
         <v>20.36</v>
       </c>
       <c r="E49" s="5">
@@ -8461,10 +8457,10 @@
       <c r="F49">
         <v>23</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G49" s="8">
         <v>17</v>
       </c>
-      <c r="H49" s="12">
+      <c r="H49" s="8">
         <v>23</v>
       </c>
       <c r="I49" t="s">
@@ -8490,11 +8486,11 @@
         <v>15.02</v>
       </c>
       <c r="C50" s="5">
-        <f>B50-L50</f>
+        <f t="shared" si="2"/>
         <v>9.6499999999999986</v>
       </c>
       <c r="D50" s="5">
-        <f>B50+L50</f>
+        <f t="shared" si="3"/>
         <v>20.39</v>
       </c>
       <c r="E50" s="5">
@@ -8503,10 +8499,10 @@
       <c r="F50">
         <v>24</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G50" s="8">
         <v>25</v>
       </c>
-      <c r="H50" s="12">
+      <c r="H50" s="8">
         <v>10</v>
       </c>
       <c r="I50" t="s">
@@ -8532,11 +8528,11 @@
         <v>15.76</v>
       </c>
       <c r="C51" s="5">
-        <f>B51-L51</f>
+        <f t="shared" si="2"/>
         <v>10.39</v>
       </c>
       <c r="D51" s="5">
-        <f>B51+L51</f>
+        <f t="shared" si="3"/>
         <v>21.13</v>
       </c>
       <c r="E51" s="5">
@@ -8545,10 +8541,10 @@
       <c r="F51">
         <v>25</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="8">
         <v>11</v>
       </c>
-      <c r="H51" s="12">
+      <c r="H51" s="8">
         <v>14</v>
       </c>
       <c r="I51" t="s">
@@ -8574,11 +8570,11 @@
         <v>7.18</v>
       </c>
       <c r="C52" s="5">
-        <f>B52-L52</f>
+        <f t="shared" si="2"/>
         <v>1.8199999999999994</v>
       </c>
       <c r="D52" s="5">
-        <f>B52+L52</f>
+        <f t="shared" si="3"/>
         <v>12.54</v>
       </c>
       <c r="E52" s="5">
@@ -8587,10 +8583,10 @@
       <c r="F52">
         <v>1</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G52" s="8">
         <v>1</v>
       </c>
-      <c r="H52" s="12">
+      <c r="H52" s="8">
         <v>5</v>
       </c>
       <c r="I52" t="s">
@@ -8616,11 +8612,11 @@
         <v>8.57</v>
       </c>
       <c r="C53" s="5">
-        <f>B53-L53</f>
+        <f t="shared" si="2"/>
         <v>3.21</v>
       </c>
       <c r="D53" s="5">
-        <f>B53+L53</f>
+        <f t="shared" si="3"/>
         <v>13.93</v>
       </c>
       <c r="E53" s="5">
@@ -8629,10 +8625,10 @@
       <c r="F53">
         <v>2</v>
       </c>
-      <c r="G53" s="12">
+      <c r="G53" s="8">
         <v>11</v>
       </c>
-      <c r="H53" s="12">
+      <c r="H53" s="8">
         <v>4</v>
       </c>
       <c r="I53" t="s">
@@ -8656,11 +8652,11 @@
         <v>8.65</v>
       </c>
       <c r="C54" s="5">
-        <f>B54-L54</f>
+        <f t="shared" si="2"/>
         <v>3.29</v>
       </c>
       <c r="D54" s="5">
-        <f>B54+L54</f>
+        <f t="shared" si="3"/>
         <v>14.010000000000002</v>
       </c>
       <c r="E54" s="5">
@@ -8669,10 +8665,10 @@
       <c r="F54">
         <v>3</v>
       </c>
-      <c r="G54" s="12">
+      <c r="G54" s="8">
         <v>2</v>
       </c>
-      <c r="H54" s="12">
+      <c r="H54" s="8">
         <v>2</v>
       </c>
       <c r="I54" t="s">
@@ -8696,11 +8692,11 @@
         <v>9.17</v>
       </c>
       <c r="C55" s="5">
-        <f>B55-L55</f>
+        <f t="shared" si="2"/>
         <v>3.8099999999999996</v>
       </c>
       <c r="D55" s="5">
-        <f>B55+L55</f>
+        <f t="shared" si="3"/>
         <v>14.530000000000001</v>
       </c>
       <c r="E55" s="5">
@@ -8709,10 +8705,10 @@
       <c r="F55">
         <v>4</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G55" s="8">
         <v>3</v>
       </c>
-      <c r="H55" s="12"/>
+      <c r="H55" s="8"/>
       <c r="I55" t="s">
         <v>81</v>
       </c>
@@ -8734,11 +8730,11 @@
         <v>9.18</v>
       </c>
       <c r="C56" s="5">
-        <f>B56-L56</f>
+        <f t="shared" si="2"/>
         <v>3.8199999999999994</v>
       </c>
       <c r="D56" s="5">
-        <f>B56+L56</f>
+        <f t="shared" si="3"/>
         <v>14.54</v>
       </c>
       <c r="E56" s="5">
@@ -8747,10 +8743,10 @@
       <c r="F56">
         <v>5</v>
       </c>
-      <c r="G56" s="12">
+      <c r="G56" s="8">
         <v>4</v>
       </c>
-      <c r="H56" s="12">
+      <c r="H56" s="8">
         <v>3</v>
       </c>
       <c r="I56" t="s">
@@ -8774,11 +8770,11 @@
         <v>9.31</v>
       </c>
       <c r="C57" s="5">
-        <f>B57-L57</f>
+        <f t="shared" si="2"/>
         <v>3.95</v>
       </c>
       <c r="D57" s="5">
-        <f>B57+L57</f>
+        <f t="shared" si="3"/>
         <v>14.670000000000002</v>
       </c>
       <c r="E57" s="5">
@@ -8787,10 +8783,10 @@
       <c r="F57">
         <v>6</v>
       </c>
-      <c r="G57" s="12">
+      <c r="G57" s="8">
         <v>5</v>
       </c>
-      <c r="H57" s="12">
+      <c r="H57" s="8">
         <v>1</v>
       </c>
       <c r="I57" t="s">
@@ -8814,11 +8810,11 @@
         <v>9.5500000000000007</v>
       </c>
       <c r="C58" s="5">
-        <f>B58-L58</f>
+        <f t="shared" si="2"/>
         <v>4.1900000000000004</v>
       </c>
       <c r="D58" s="5">
-        <f>B58+L58</f>
+        <f t="shared" si="3"/>
         <v>14.91</v>
       </c>
       <c r="E58" s="5">
@@ -8827,10 +8823,10 @@
       <c r="F58">
         <v>7</v>
       </c>
-      <c r="G58" s="12">
+      <c r="G58" s="8">
         <v>6</v>
       </c>
-      <c r="H58" s="12">
+      <c r="H58" s="8">
         <v>15</v>
       </c>
       <c r="I58" t="s">
@@ -8854,11 +8850,11 @@
         <v>9.65</v>
       </c>
       <c r="C59" s="5">
-        <f>B59-L59</f>
+        <f t="shared" si="2"/>
         <v>4.29</v>
       </c>
       <c r="D59" s="5">
-        <f>B59+L59</f>
+        <f t="shared" si="3"/>
         <v>15.010000000000002</v>
       </c>
       <c r="E59" s="5">
@@ -8867,10 +8863,10 @@
       <c r="F59">
         <v>8</v>
       </c>
-      <c r="G59" s="12">
+      <c r="G59" s="8">
         <v>7</v>
       </c>
-      <c r="H59" s="12">
+      <c r="H59" s="8">
         <v>8</v>
       </c>
       <c r="I59" t="s">
@@ -8894,11 +8890,11 @@
         <v>10.06</v>
       </c>
       <c r="C60" s="5">
-        <f>B60-L60</f>
+        <f t="shared" si="2"/>
         <v>4.7</v>
       </c>
       <c r="D60" s="5">
-        <f>B60+L60</f>
+        <f t="shared" si="3"/>
         <v>15.420000000000002</v>
       </c>
       <c r="E60" s="5">
@@ -8907,10 +8903,10 @@
       <c r="F60">
         <v>9</v>
       </c>
-      <c r="G60" s="12">
+      <c r="G60" s="8">
         <v>12</v>
       </c>
-      <c r="H60" s="12">
+      <c r="H60" s="8">
         <v>10</v>
       </c>
       <c r="I60" t="s">
@@ -8934,11 +8930,11 @@
         <v>10.72</v>
       </c>
       <c r="C61" s="5">
-        <f>B61-L61</f>
+        <f t="shared" si="2"/>
         <v>5.36</v>
       </c>
       <c r="D61" s="5">
-        <f>B61+L61</f>
+        <f t="shared" si="3"/>
         <v>16.080000000000002</v>
       </c>
       <c r="E61" s="5">
@@ -8947,10 +8943,10 @@
       <c r="F61">
         <v>10</v>
       </c>
-      <c r="G61" s="12">
+      <c r="G61" s="8">
         <v>8</v>
       </c>
-      <c r="H61" s="12">
+      <c r="H61" s="8">
         <v>6</v>
       </c>
       <c r="I61" t="s">
@@ -8974,11 +8970,11 @@
         <v>10.73</v>
       </c>
       <c r="C62" s="5">
-        <f>B62-L62</f>
+        <f t="shared" si="2"/>
         <v>5.37</v>
       </c>
       <c r="D62" s="5">
-        <f>B62+L62</f>
+        <f t="shared" si="3"/>
         <v>16.09</v>
       </c>
       <c r="E62" s="5">
@@ -8987,10 +8983,10 @@
       <c r="F62">
         <v>11</v>
       </c>
-      <c r="G62" s="12">
+      <c r="G62" s="8">
         <v>9</v>
       </c>
-      <c r="H62" s="12">
+      <c r="H62" s="8">
         <v>7</v>
       </c>
       <c r="I62" t="s">
@@ -9014,11 +9010,11 @@
         <v>11.14</v>
       </c>
       <c r="C63" s="5">
-        <f>B63-L63</f>
+        <f t="shared" si="2"/>
         <v>5.78</v>
       </c>
       <c r="D63" s="5">
-        <f>B63+L63</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
       <c r="E63" s="5">
@@ -9027,10 +9023,10 @@
       <c r="F63">
         <v>12</v>
       </c>
-      <c r="G63" s="12">
+      <c r="G63" s="8">
         <v>13</v>
       </c>
-      <c r="H63" s="12">
+      <c r="H63" s="8">
         <v>9</v>
       </c>
       <c r="I63" t="s">
@@ -9054,11 +9050,11 @@
         <v>11.24</v>
       </c>
       <c r="C64" s="5">
-        <f>B64-L64</f>
+        <f t="shared" si="2"/>
         <v>5.88</v>
       </c>
       <c r="D64" s="5">
-        <f>B64+L64</f>
+        <f t="shared" si="3"/>
         <v>16.600000000000001</v>
       </c>
       <c r="E64" s="5">
@@ -9067,10 +9063,10 @@
       <c r="F64">
         <v>13</v>
       </c>
-      <c r="G64" s="12">
+      <c r="G64" s="8">
         <v>14</v>
       </c>
-      <c r="H64" s="12">
+      <c r="H64" s="8">
         <v>11</v>
       </c>
       <c r="I64" t="s">
@@ -9086,7 +9082,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>42</v>
       </c>
@@ -9094,11 +9090,11 @@
         <v>12.25</v>
       </c>
       <c r="C65" s="5">
-        <f>B65-L65</f>
+        <f t="shared" si="2"/>
         <v>6.89</v>
       </c>
       <c r="D65" s="5">
-        <f>B65+L65</f>
+        <f t="shared" si="3"/>
         <v>17.61</v>
       </c>
       <c r="E65" s="5">
@@ -9107,10 +9103,10 @@
       <c r="F65">
         <v>14</v>
       </c>
-      <c r="G65" s="12">
+      <c r="G65" s="8">
         <v>18</v>
       </c>
-      <c r="H65" s="12">
+      <c r="H65" s="8">
         <v>25</v>
       </c>
       <c r="I65" t="s">
@@ -9126,7 +9122,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>48</v>
       </c>
@@ -9134,11 +9130,11 @@
         <v>12.39</v>
       </c>
       <c r="C66" s="5">
-        <f>B66-L66</f>
+        <f t="shared" ref="C66:C97" si="4">B66-L66</f>
         <v>7.03</v>
       </c>
       <c r="D66" s="5">
-        <f>B66+L66</f>
+        <f t="shared" ref="D66:D101" si="5">B66+L66</f>
         <v>17.75</v>
       </c>
       <c r="E66" s="5">
@@ -9147,10 +9143,10 @@
       <c r="F66">
         <v>15</v>
       </c>
-      <c r="G66" s="12">
+      <c r="G66" s="8">
         <v>10</v>
       </c>
-      <c r="H66" s="12">
+      <c r="H66" s="8">
         <v>19</v>
       </c>
       <c r="I66" t="s">
@@ -9166,7 +9162,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -9174,11 +9170,11 @@
         <v>13.02</v>
       </c>
       <c r="C67" s="5">
-        <f>B67-L67</f>
+        <f t="shared" si="4"/>
         <v>7.6599999999999993</v>
       </c>
       <c r="D67" s="5">
-        <f>B67+L67</f>
+        <f t="shared" si="5"/>
         <v>18.38</v>
       </c>
       <c r="E67" s="5">
@@ -9187,10 +9183,10 @@
       <c r="F67">
         <v>16</v>
       </c>
-      <c r="G67" s="12">
+      <c r="G67" s="8">
         <v>15</v>
       </c>
-      <c r="H67" s="12">
+      <c r="H67" s="8">
         <v>13</v>
       </c>
       <c r="I67" t="s">
@@ -9206,7 +9202,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>31</v>
       </c>
@@ -9214,11 +9210,11 @@
         <v>13.16</v>
       </c>
       <c r="C68" s="5">
-        <f>B68-L68</f>
+        <f t="shared" si="4"/>
         <v>7.8</v>
       </c>
       <c r="D68" s="5">
-        <f>B68+L68</f>
+        <f t="shared" si="5"/>
         <v>18.52</v>
       </c>
       <c r="E68" s="5">
@@ -9227,10 +9223,10 @@
       <c r="F68">
         <v>17</v>
       </c>
-      <c r="G68" s="12">
+      <c r="G68" s="8">
         <v>16</v>
       </c>
-      <c r="H68" s="12">
+      <c r="H68" s="8">
         <v>23</v>
       </c>
       <c r="I68" t="s">
@@ -9246,7 +9242,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>41</v>
       </c>
@@ -9254,11 +9250,11 @@
         <v>13.66</v>
       </c>
       <c r="C69" s="5">
-        <f>B69-L69</f>
+        <f t="shared" si="4"/>
         <v>8.3000000000000007</v>
       </c>
       <c r="D69" s="5">
-        <f>B69+L69</f>
+        <f t="shared" si="5"/>
         <v>19.02</v>
       </c>
       <c r="E69" s="5">
@@ -9267,10 +9263,10 @@
       <c r="F69">
         <v>18</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="8">
         <v>17</v>
       </c>
-      <c r="H69" s="12">
+      <c r="H69" s="8">
         <v>18</v>
       </c>
       <c r="I69" t="s">
@@ -9286,7 +9282,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>29</v>
       </c>
@@ -9294,11 +9290,11 @@
         <v>14.2</v>
       </c>
       <c r="C70" s="5">
-        <f>B70-L70</f>
+        <f t="shared" si="4"/>
         <v>8.84</v>
       </c>
       <c r="D70" s="5">
-        <f>B70+L70</f>
+        <f t="shared" si="5"/>
         <v>19.559999999999999</v>
       </c>
       <c r="E70" s="5">
@@ -9307,10 +9303,10 @@
       <c r="F70">
         <v>19</v>
       </c>
-      <c r="G70" s="12">
+      <c r="G70" s="8">
         <v>19</v>
       </c>
-      <c r="H70" s="12">
+      <c r="H70" s="8">
         <v>17</v>
       </c>
       <c r="I70" t="s">
@@ -9326,7 +9322,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>49</v>
       </c>
@@ -9334,11 +9330,11 @@
         <v>14.4</v>
       </c>
       <c r="C71" s="5">
-        <f>B71-L71</f>
+        <f t="shared" si="4"/>
         <v>9.0399999999999991</v>
       </c>
       <c r="D71" s="5">
-        <f>B71+L71</f>
+        <f t="shared" si="5"/>
         <v>19.760000000000002</v>
       </c>
       <c r="E71" s="5">
@@ -9347,10 +9343,10 @@
       <c r="F71">
         <v>20</v>
       </c>
-      <c r="G71" s="12">
+      <c r="G71" s="8">
         <v>20</v>
       </c>
-      <c r="H71" s="12">
+      <c r="H71" s="8">
         <v>14</v>
       </c>
       <c r="I71" t="s">
@@ -9366,7 +9362,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>47</v>
       </c>
@@ -9374,11 +9370,11 @@
         <v>15.16</v>
       </c>
       <c r="C72" s="5">
-        <f>B72-L72</f>
+        <f t="shared" si="4"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="D72" s="5">
-        <f>B72+L72</f>
+        <f t="shared" si="5"/>
         <v>20.52</v>
       </c>
       <c r="E72" s="5">
@@ -9387,10 +9383,10 @@
       <c r="F72">
         <v>21</v>
       </c>
-      <c r="G72" s="12">
+      <c r="G72" s="8">
         <v>21</v>
       </c>
-      <c r="H72" s="12">
+      <c r="H72" s="8">
         <v>24</v>
       </c>
       <c r="I72" t="s">
@@ -9406,7 +9402,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>32</v>
       </c>
@@ -9414,11 +9410,11 @@
         <v>15.34</v>
       </c>
       <c r="C73" s="5">
-        <f>B73-L73</f>
+        <f t="shared" si="4"/>
         <v>9.98</v>
       </c>
       <c r="D73" s="5">
-        <f>B73+L73</f>
+        <f t="shared" si="5"/>
         <v>20.7</v>
       </c>
       <c r="E73" s="5">
@@ -9427,10 +9423,10 @@
       <c r="F73">
         <v>22</v>
       </c>
-      <c r="G73" s="12">
+      <c r="G73" s="8">
         <v>22</v>
       </c>
-      <c r="H73" s="12">
+      <c r="H73" s="8">
         <v>16</v>
       </c>
       <c r="I73" t="s">
@@ -9446,7 +9442,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>26</v>
       </c>
@@ -9454,11 +9450,11 @@
         <v>15.57</v>
       </c>
       <c r="C74" s="5">
-        <f>B74-L74</f>
+        <f t="shared" si="4"/>
         <v>10.210000000000001</v>
       </c>
       <c r="D74" s="5">
-        <f>B74+L74</f>
+        <f t="shared" si="5"/>
         <v>20.93</v>
       </c>
       <c r="E74" s="5">
@@ -9467,10 +9463,10 @@
       <c r="F74">
         <v>23</v>
       </c>
-      <c r="G74" s="12">
+      <c r="G74" s="8">
         <v>23</v>
       </c>
-      <c r="H74" s="12">
+      <c r="H74" s="8">
         <v>12</v>
       </c>
       <c r="I74" t="s">
@@ -9486,7 +9482,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>46</v>
       </c>
@@ -9494,11 +9490,11 @@
         <v>16.53</v>
       </c>
       <c r="C75" s="5">
-        <f>B75-L75</f>
+        <f t="shared" si="4"/>
         <v>11.170000000000002</v>
       </c>
       <c r="D75" s="5">
-        <f>B75+L75</f>
+        <f t="shared" si="5"/>
         <v>21.89</v>
       </c>
       <c r="E75" s="5">
@@ -9507,10 +9503,10 @@
       <c r="F75">
         <v>24</v>
       </c>
-      <c r="G75" s="12">
+      <c r="G75" s="8">
         <v>24</v>
       </c>
-      <c r="H75" s="12">
+      <c r="H75" s="8">
         <v>22</v>
       </c>
       <c r="I75" t="s">
@@ -9526,7 +9522,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>43</v>
       </c>
@@ -9534,11 +9530,11 @@
         <v>17.59</v>
       </c>
       <c r="C76" s="5">
-        <f>B76-L76</f>
+        <f t="shared" si="4"/>
         <v>12.23</v>
       </c>
       <c r="D76" s="5">
-        <f>B76+L76</f>
+        <f t="shared" si="5"/>
         <v>22.95</v>
       </c>
       <c r="E76" s="5">
@@ -9547,10 +9543,10 @@
       <c r="F76">
         <v>25</v>
       </c>
-      <c r="G76" s="12">
+      <c r="G76" s="8">
         <v>25</v>
       </c>
-      <c r="H76" s="12">
+      <c r="H76" s="8">
         <v>21</v>
       </c>
       <c r="I76" t="s">
@@ -9566,22 +9562,33 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="5"/>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" s="6">
+        <v>5.63</v>
+      </c>
       <c r="C77" s="5">
-        <f>B77-L77</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>0.42999999999999972</v>
       </c>
       <c r="D77" s="5">
-        <f>B77+L77</f>
-        <v>5.2</v>
-      </c>
-      <c r="E77" s="5"/>
+        <f t="shared" si="5"/>
+        <v>10.83</v>
+      </c>
+      <c r="E77" s="5">
+        <v>0.43</v>
+      </c>
       <c r="F77">
         <v>1</v>
       </c>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
+      <c r="G77" s="8">
+        <v>1</v>
+      </c>
+      <c r="H77" s="8">
+        <v>1</v>
+      </c>
       <c r="I77" t="s">
         <v>75</v>
       </c>
@@ -9595,22 +9602,33 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="5"/>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" s="6">
+        <v>7.95</v>
+      </c>
       <c r="C78" s="5">
-        <f>B78-L78</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>2.75</v>
       </c>
       <c r="D78" s="5">
-        <f>B78+L78</f>
-        <v>5.2</v>
-      </c>
-      <c r="E78" s="5"/>
+        <f t="shared" si="5"/>
+        <v>13.15</v>
+      </c>
+      <c r="E78" s="5">
+        <v>7.95</v>
+      </c>
       <c r="F78">
         <v>2</v>
       </c>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
+      <c r="G78" s="8">
+        <v>8</v>
+      </c>
+      <c r="H78" s="8">
+        <v>6</v>
+      </c>
       <c r="I78" t="s">
         <v>75</v>
       </c>
@@ -9623,23 +9641,36 @@
       <c r="L78" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="5"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="5"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79" s="6">
+        <v>8.39</v>
+      </c>
       <c r="C79" s="5">
-        <f>B79-L79</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>3.1900000000000004</v>
       </c>
       <c r="D79" s="5">
-        <f>B79+L79</f>
-        <v>5.2</v>
-      </c>
-      <c r="E79" s="5"/>
+        <f t="shared" si="5"/>
+        <v>13.59</v>
+      </c>
+      <c r="E79" s="5">
+        <v>3.19</v>
+      </c>
       <c r="F79">
         <v>3</v>
       </c>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
+      <c r="G79" s="8">
+        <v>2</v>
+      </c>
+      <c r="H79" s="8">
+        <v>4</v>
+      </c>
       <c r="I79" t="s">
         <v>75</v>
       </c>
@@ -9652,23 +9683,36 @@
       <c r="L79" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="5"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="5"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B80" s="6">
+        <v>8.5</v>
+      </c>
       <c r="C80" s="5">
-        <f>B80-L80</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>3.3</v>
       </c>
       <c r="D80" s="5">
-        <f>B80+L80</f>
-        <v>5.2</v>
-      </c>
-      <c r="E80" s="5"/>
+        <f t="shared" si="5"/>
+        <v>13.7</v>
+      </c>
+      <c r="E80" s="5">
+        <v>3.3</v>
+      </c>
       <c r="F80">
         <v>4</v>
       </c>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
+      <c r="G80" s="8">
+        <v>3</v>
+      </c>
+      <c r="H80" s="8">
+        <v>5</v>
+      </c>
       <c r="I80" t="s">
         <v>75</v>
       </c>
@@ -9681,23 +9725,36 @@
       <c r="L80" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="5"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="5"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" s="6">
+        <v>8.82</v>
+      </c>
       <c r="C81" s="5">
-        <f>B81-L81</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>3.62</v>
       </c>
       <c r="D81" s="5">
-        <f>B81+L81</f>
-        <v>5.2</v>
-      </c>
-      <c r="E81" s="5"/>
+        <f t="shared" si="5"/>
+        <v>14.02</v>
+      </c>
+      <c r="E81" s="5">
+        <v>8.82</v>
+      </c>
       <c r="F81">
         <v>5</v>
       </c>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12"/>
+      <c r="G81" s="8">
+        <v>9</v>
+      </c>
+      <c r="H81" s="8">
+        <v>7</v>
+      </c>
       <c r="I81" t="s">
         <v>75</v>
       </c>
@@ -9710,23 +9767,36 @@
       <c r="L81" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="5"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="5"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B82" s="6">
+        <v>9.2100000000000009</v>
+      </c>
       <c r="C82" s="5">
-        <f>B82-L82</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>4.0100000000000007</v>
       </c>
       <c r="D82" s="5">
-        <f>B82+L82</f>
-        <v>5.2</v>
-      </c>
-      <c r="E82" s="5"/>
+        <f t="shared" si="5"/>
+        <v>14.41</v>
+      </c>
+      <c r="E82" s="5">
+        <v>4.01</v>
+      </c>
       <c r="F82">
         <v>6</v>
       </c>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12"/>
+      <c r="G82" s="8">
+        <v>4</v>
+      </c>
+      <c r="H82" s="8">
+        <v>2</v>
+      </c>
       <c r="I82" t="s">
         <v>75</v>
       </c>
@@ -9739,23 +9809,36 @@
       <c r="L82" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="5"/>
+      <c r="N82" s="6"/>
+      <c r="O82" s="5"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B83" s="6">
+        <v>9.26</v>
+      </c>
       <c r="C83" s="5">
-        <f>B83-L83</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>4.0599999999999996</v>
       </c>
       <c r="D83" s="5">
-        <f>B83+L83</f>
-        <v>5.2</v>
-      </c>
-      <c r="E83" s="5"/>
+        <f t="shared" si="5"/>
+        <v>14.46</v>
+      </c>
+      <c r="E83" s="5">
+        <v>9.26</v>
+      </c>
       <c r="F83">
         <v>7</v>
       </c>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12"/>
+      <c r="G83" s="8">
+        <v>10</v>
+      </c>
+      <c r="H83" s="8">
+        <v>3</v>
+      </c>
       <c r="I83" t="s">
         <v>75</v>
       </c>
@@ -9768,23 +9851,36 @@
       <c r="L83" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="5"/>
+      <c r="N83" s="6"/>
+      <c r="O83" s="5"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B84" s="6">
+        <v>9.27</v>
+      </c>
       <c r="C84" s="5">
-        <f>B84-L84</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>4.0699999999999994</v>
       </c>
       <c r="D84" s="5">
-        <f>B84+L84</f>
-        <v>5.2</v>
-      </c>
-      <c r="E84" s="5"/>
+        <f t="shared" si="5"/>
+        <v>14.469999999999999</v>
+      </c>
+      <c r="E84" s="5">
+        <v>9.27</v>
+      </c>
       <c r="F84">
         <v>8</v>
       </c>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12"/>
+      <c r="G84" s="8">
+        <v>11</v>
+      </c>
+      <c r="H84" s="8">
+        <v>10</v>
+      </c>
       <c r="I84" t="s">
         <v>75</v>
       </c>
@@ -9797,23 +9893,36 @@
       <c r="L84" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="5"/>
+      <c r="N84" s="6"/>
+      <c r="O84" s="5"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B85" s="6">
+        <v>9.3000000000000007</v>
+      </c>
       <c r="C85" s="5">
-        <f>B85-L85</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>4.1000000000000005</v>
       </c>
       <c r="D85" s="5">
-        <f>B85+L85</f>
-        <v>5.2</v>
-      </c>
-      <c r="E85" s="5"/>
+        <f t="shared" si="5"/>
+        <v>14.5</v>
+      </c>
+      <c r="E85" s="5">
+        <v>9.3000000000000007</v>
+      </c>
       <c r="F85">
         <v>9</v>
       </c>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12"/>
+      <c r="G85" s="8">
+        <v>12</v>
+      </c>
+      <c r="H85" s="8">
+        <v>16</v>
+      </c>
       <c r="I85" t="s">
         <v>75</v>
       </c>
@@ -9826,23 +9935,36 @@
       <c r="L85" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="5"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="5"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B86" s="6">
+        <v>9.52</v>
+      </c>
       <c r="C86" s="5">
-        <f>B86-L86</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>4.3199999999999994</v>
       </c>
       <c r="D86" s="5">
-        <f>B86+L86</f>
-        <v>5.2</v>
-      </c>
-      <c r="E86" s="5"/>
+        <f t="shared" si="5"/>
+        <v>14.719999999999999</v>
+      </c>
+      <c r="E86" s="5">
+        <v>4.32</v>
+      </c>
       <c r="F86">
         <v>10</v>
       </c>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12"/>
+      <c r="G86" s="8">
+        <v>5</v>
+      </c>
+      <c r="H86" s="8">
+        <v>17</v>
+      </c>
       <c r="I86" t="s">
         <v>75</v>
       </c>
@@ -9855,23 +9977,36 @@
       <c r="L86" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="5"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="5"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="6">
+        <v>10.9</v>
+      </c>
       <c r="C87" s="5">
-        <f>B87-L87</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>5.7</v>
       </c>
       <c r="D87" s="5">
-        <f>B87+L87</f>
-        <v>5.2</v>
-      </c>
-      <c r="E87" s="5"/>
+        <f t="shared" si="5"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E87" s="5">
+        <v>10.9</v>
+      </c>
       <c r="F87">
         <v>11</v>
       </c>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12"/>
+      <c r="G87" s="8">
+        <v>13</v>
+      </c>
+      <c r="H87" s="8">
+        <v>11</v>
+      </c>
       <c r="I87" t="s">
         <v>75</v>
       </c>
@@ -9884,23 +10019,36 @@
       <c r="L87" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" s="5"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="5"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88" s="6">
+        <v>11.44</v>
+      </c>
       <c r="C88" s="5">
-        <f>B88-L88</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>6.2399999999999993</v>
       </c>
       <c r="D88" s="5">
-        <f>B88+L88</f>
-        <v>5.2</v>
-      </c>
-      <c r="E88" s="5"/>
+        <f t="shared" si="5"/>
+        <v>16.64</v>
+      </c>
+      <c r="E88" s="5">
+        <v>11.44</v>
+      </c>
       <c r="F88">
         <v>12</v>
       </c>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12"/>
+      <c r="G88" s="8">
+        <v>14</v>
+      </c>
+      <c r="H88" s="8">
+        <v>9</v>
+      </c>
       <c r="I88" t="s">
         <v>75</v>
       </c>
@@ -9913,23 +10061,36 @@
       <c r="L88" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" s="5"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="5"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" s="6">
+        <v>11.89</v>
+      </c>
       <c r="C89" s="5">
-        <f>B89-L89</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>6.69</v>
       </c>
       <c r="D89" s="5">
-        <f>B89+L89</f>
-        <v>5.2</v>
-      </c>
-      <c r="E89" s="5"/>
+        <f t="shared" si="5"/>
+        <v>17.09</v>
+      </c>
+      <c r="E89" s="5">
+        <v>6.69</v>
+      </c>
       <c r="F89">
         <v>13</v>
       </c>
-      <c r="G89" s="12"/>
-      <c r="H89" s="12"/>
+      <c r="G89" s="8">
+        <v>6</v>
+      </c>
+      <c r="H89" s="8">
+        <v>15</v>
+      </c>
       <c r="I89" t="s">
         <v>75</v>
       </c>
@@ -9942,23 +10103,36 @@
       <c r="L89" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="5"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="5"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B90" s="6">
+        <v>12.26</v>
+      </c>
       <c r="C90" s="5">
-        <f>B90-L90</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>7.06</v>
       </c>
       <c r="D90" s="5">
-        <f>B90+L90</f>
-        <v>5.2</v>
-      </c>
-      <c r="E90" s="5"/>
+        <f t="shared" si="5"/>
+        <v>17.46</v>
+      </c>
+      <c r="E90" s="5">
+        <v>12.26</v>
+      </c>
       <c r="F90">
         <v>14</v>
       </c>
-      <c r="G90" s="12"/>
-      <c r="H90" s="12"/>
+      <c r="G90" s="8">
+        <v>16</v>
+      </c>
+      <c r="H90" s="8">
+        <v>8</v>
+      </c>
       <c r="I90" t="s">
         <v>75</v>
       </c>
@@ -9971,23 +10145,36 @@
       <c r="L90" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="5"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="5"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B91" s="6">
+        <v>12.39</v>
+      </c>
       <c r="C91" s="5">
-        <f>B91-L91</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>7.19</v>
       </c>
       <c r="D91" s="5">
-        <f>B91+L91</f>
-        <v>5.2</v>
-      </c>
-      <c r="E91" s="5"/>
+        <f t="shared" si="5"/>
+        <v>17.59</v>
+      </c>
+      <c r="E91" s="5">
+        <v>7.19</v>
+      </c>
       <c r="F91">
         <v>15</v>
       </c>
-      <c r="G91" s="12"/>
-      <c r="H91" s="12"/>
+      <c r="G91" s="8">
+        <v>7</v>
+      </c>
+      <c r="H91" s="8">
+        <v>12</v>
+      </c>
       <c r="I91" t="s">
         <v>75</v>
       </c>
@@ -10000,23 +10187,36 @@
       <c r="L91" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="5"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="5"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B92" s="6">
+        <v>12.74</v>
+      </c>
       <c r="C92" s="5">
-        <f>B92-L92</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>7.54</v>
       </c>
       <c r="D92" s="5">
-        <f>B92+L92</f>
-        <v>5.2</v>
-      </c>
-      <c r="E92" s="5"/>
+        <f t="shared" si="5"/>
+        <v>17.940000000000001</v>
+      </c>
+      <c r="E92" s="5">
+        <v>12.74</v>
+      </c>
       <c r="F92">
         <v>16</v>
       </c>
-      <c r="G92" s="12"/>
-      <c r="H92" s="12"/>
+      <c r="G92" s="8">
+        <v>17</v>
+      </c>
+      <c r="H92" s="8">
+        <v>13</v>
+      </c>
       <c r="I92" t="s">
         <v>75</v>
       </c>
@@ -10029,23 +10229,36 @@
       <c r="L92" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B93" s="5"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="5"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B93" s="6">
+        <v>12.78</v>
+      </c>
       <c r="C93" s="5">
-        <f>B93-L93</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>7.5799999999999992</v>
       </c>
       <c r="D93" s="5">
-        <f>B93+L93</f>
-        <v>5.2</v>
-      </c>
-      <c r="E93" s="5"/>
+        <f t="shared" si="5"/>
+        <v>17.98</v>
+      </c>
+      <c r="E93" s="5">
+        <v>17.98</v>
+      </c>
       <c r="F93">
         <v>17</v>
       </c>
-      <c r="G93" s="12"/>
-      <c r="H93" s="12"/>
+      <c r="G93" s="8">
+        <v>22</v>
+      </c>
+      <c r="H93" s="8">
+        <v>20</v>
+      </c>
       <c r="I93" t="s">
         <v>75</v>
       </c>
@@ -10058,23 +10271,36 @@
       <c r="L93" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="5"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="5"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B94" s="6">
+        <v>13.64</v>
+      </c>
       <c r="C94" s="5">
-        <f>B94-L94</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>8.4400000000000013</v>
       </c>
       <c r="D94" s="5">
-        <f>B94+L94</f>
-        <v>5.2</v>
-      </c>
-      <c r="E94" s="5"/>
+        <f t="shared" si="5"/>
+        <v>18.84</v>
+      </c>
+      <c r="E94" s="5">
+        <v>13.64</v>
+      </c>
       <c r="F94">
         <v>18</v>
       </c>
-      <c r="G94" s="12"/>
-      <c r="H94" s="12"/>
+      <c r="G94" s="8">
+        <v>18</v>
+      </c>
+      <c r="H94" s="8">
+        <v>14</v>
+      </c>
       <c r="I94" t="s">
         <v>75</v>
       </c>
@@ -10087,23 +10313,36 @@
       <c r="L94" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="5"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="5"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B95" s="6">
+        <v>13.75</v>
+      </c>
       <c r="C95" s="5">
-        <f>B95-L95</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>8.5500000000000007</v>
       </c>
       <c r="D95" s="5">
-        <f>B95+L95</f>
-        <v>5.2</v>
-      </c>
-      <c r="E95" s="5"/>
+        <f t="shared" si="5"/>
+        <v>18.95</v>
+      </c>
+      <c r="E95" s="5">
+        <v>18.95</v>
+      </c>
       <c r="F95">
         <v>19</v>
       </c>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
+      <c r="G95" s="8">
+        <v>23</v>
+      </c>
+      <c r="H95" s="8">
+        <v>19</v>
+      </c>
       <c r="I95" t="s">
         <v>75</v>
       </c>
@@ -10116,23 +10355,36 @@
       <c r="L95" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="5"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="5"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B96" s="6">
+        <v>14.11</v>
+      </c>
       <c r="C96" s="5">
-        <f>B96-L96</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>8.91</v>
       </c>
       <c r="D96" s="5">
-        <f>B96+L96</f>
-        <v>5.2</v>
-      </c>
-      <c r="E96" s="5"/>
+        <f t="shared" si="5"/>
+        <v>19.309999999999999</v>
+      </c>
+      <c r="E96" s="5">
+        <v>19.309999999999999</v>
+      </c>
       <c r="F96">
         <v>20</v>
       </c>
-      <c r="G96" s="12"/>
-      <c r="H96" s="12"/>
+      <c r="G96" s="8">
+        <v>24</v>
+      </c>
+      <c r="H96" s="8">
+        <v>18</v>
+      </c>
       <c r="I96" t="s">
         <v>75</v>
       </c>
@@ -10145,23 +10397,36 @@
       <c r="L96" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="5"/>
+      <c r="N96" s="6"/>
+      <c r="O96" s="5"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" s="6">
+        <v>15.58</v>
+      </c>
       <c r="C97" s="5">
-        <f>B97-L97</f>
-        <v>-5.2</v>
+        <f t="shared" si="4"/>
+        <v>10.379999999999999</v>
       </c>
       <c r="D97" s="5">
-        <f>B97+L97</f>
-        <v>5.2</v>
-      </c>
-      <c r="E97" s="5"/>
+        <f t="shared" si="5"/>
+        <v>20.78</v>
+      </c>
+      <c r="E97" s="5">
+        <v>15.58</v>
+      </c>
       <c r="F97">
         <v>21</v>
       </c>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12"/>
+      <c r="G97" s="8">
+        <v>19</v>
+      </c>
+      <c r="H97" s="8">
+        <v>25</v>
+      </c>
       <c r="I97" t="s">
         <v>75</v>
       </c>
@@ -10174,23 +10439,36 @@
       <c r="L97" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="5"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="5"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B98" s="6">
+        <v>16.14</v>
+      </c>
       <c r="C98" s="5">
-        <f>B98-L98</f>
-        <v>-5.2</v>
+        <f t="shared" ref="C98:C101" si="6">B98-L98</f>
+        <v>10.940000000000001</v>
       </c>
       <c r="D98" s="5">
-        <f>B98+L98</f>
-        <v>5.2</v>
-      </c>
-      <c r="E98" s="5"/>
+        <f t="shared" si="5"/>
+        <v>21.34</v>
+      </c>
+      <c r="E98" s="5">
+        <v>16.14</v>
+      </c>
       <c r="F98">
         <v>22</v>
       </c>
-      <c r="G98" s="12"/>
-      <c r="H98" s="12"/>
+      <c r="G98" s="8">
+        <v>20</v>
+      </c>
+      <c r="H98" s="8">
+        <v>24</v>
+      </c>
       <c r="I98" t="s">
         <v>75</v>
       </c>
@@ -10203,23 +10481,36 @@
       <c r="L98" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="5"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="5"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B99" s="6">
+        <v>16.88</v>
+      </c>
       <c r="C99" s="5">
-        <f>B99-L99</f>
-        <v>-5.2</v>
+        <f t="shared" si="6"/>
+        <v>11.68</v>
       </c>
       <c r="D99" s="5">
-        <f>B99+L99</f>
-        <v>5.2</v>
-      </c>
-      <c r="E99" s="5"/>
+        <f t="shared" si="5"/>
+        <v>22.08</v>
+      </c>
+      <c r="E99" s="5">
+        <v>16.88</v>
+      </c>
       <c r="F99">
         <v>23</v>
       </c>
-      <c r="G99" s="12"/>
-      <c r="H99" s="12"/>
+      <c r="G99" s="8">
+        <v>21</v>
+      </c>
+      <c r="H99" s="8">
+        <v>23</v>
+      </c>
       <c r="I99" t="s">
         <v>75</v>
       </c>
@@ -10232,23 +10523,36 @@
       <c r="L99" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="5"/>
+      <c r="N99" s="6"/>
+      <c r="O99" s="5"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B100" s="6">
+        <v>17.329999999999998</v>
+      </c>
       <c r="C100" s="5">
-        <f>B100-L100</f>
-        <v>-5.2</v>
+        <f t="shared" si="6"/>
+        <v>12.129999999999999</v>
       </c>
       <c r="D100" s="5">
-        <f>B100+L100</f>
-        <v>5.2</v>
-      </c>
-      <c r="E100" s="5"/>
+        <f t="shared" si="5"/>
+        <v>22.529999999999998</v>
+      </c>
+      <c r="E100" s="5">
+        <v>12.13</v>
+      </c>
       <c r="F100">
         <v>24</v>
       </c>
-      <c r="G100" s="12"/>
-      <c r="H100" s="12"/>
+      <c r="G100" s="8">
+        <v>15</v>
+      </c>
+      <c r="H100" s="8">
+        <v>21</v>
+      </c>
       <c r="I100" t="s">
         <v>75</v>
       </c>
@@ -10261,23 +10565,36 @@
       <c r="L100" s="5">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="5"/>
+      <c r="N100" s="6"/>
+      <c r="O100" s="5"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B101" s="6">
+        <v>17.54</v>
+      </c>
       <c r="C101" s="5">
-        <f>B101-L101</f>
-        <v>-5.2</v>
+        <f t="shared" si="6"/>
+        <v>12.34</v>
       </c>
       <c r="D101" s="5">
-        <f>B101+L101</f>
-        <v>5.2</v>
-      </c>
-      <c r="E101" s="5"/>
+        <f t="shared" si="5"/>
+        <v>22.74</v>
+      </c>
+      <c r="E101" s="5">
+        <v>22.74</v>
+      </c>
       <c r="F101">
         <v>25</v>
       </c>
-      <c r="G101" s="12"/>
-      <c r="H101" s="12"/>
+      <c r="G101" s="8">
+        <v>25</v>
+      </c>
+      <c r="H101" s="8">
+        <v>22</v>
+      </c>
       <c r="I101" t="s">
         <v>75</v>
       </c>
@@ -10290,10 +10607,16 @@
       <c r="L101" s="5">
         <v>5.2</v>
       </c>
+      <c r="N101" s="6"/>
+      <c r="O101" s="5"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="N102" s="6"/>
+      <c r="O102" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N27:O51">
-    <sortCondition ref="O27:O51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N78:O102">
+    <sortCondition ref="O102"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="landscape" r:id="rId1"/>

--- a/predictions/model_compare.xlsx
+++ b/predictions/model_compare.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ripa_\Desktop\Programing\IndyCar_Project\predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2B043F-FAC7-4114-98E9-A1461423C0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B42EB2C-9579-43C0-B0C1-CA365EA78B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{74EB7EE7-EB5C-4423-87E4-FE46F1C4926A}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{74EB7EE7-EB5C-4423-87E4-FE46F1C4926A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pre-Qualy" sheetId="1" r:id="rId1"/>
-    <sheet name="Post-Qualy" sheetId="2" r:id="rId2"/>
+    <sheet name="Pre-Qualy_Model" sheetId="1" r:id="rId1"/>
+    <sheet name="Post-Qualy_Model" sheetId="2" r:id="rId2"/>
     <sheet name="Pre-Qualy Results" sheetId="3" r:id="rId3"/>
     <sheet name="Post-Qualy Results" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -2333,7 +2333,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E126BF-468F-45B0-90F5-005D8BFD087E}">
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q357"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="17.20703125" bestFit="1" customWidth="1"/>
@@ -2413,7 +2413,7 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="8">
         <v>1</v>
       </c>
       <c r="I2" t="s">
@@ -2454,7 +2454,7 @@
       <c r="G3">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="8">
         <v>23</v>
       </c>
       <c r="I3" t="s">
@@ -2495,7 +2495,7 @@
       <c r="G4">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="8">
         <v>2</v>
       </c>
       <c r="I4" t="s">
@@ -2536,7 +2536,7 @@
       <c r="G5">
         <v>10</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="8">
         <v>7</v>
       </c>
       <c r="I5" t="s">
@@ -2577,7 +2577,7 @@
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="8">
         <v>4</v>
       </c>
       <c r="I6" t="s">
@@ -2618,7 +2618,7 @@
       <c r="G7">
         <v>5</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="8">
         <v>5</v>
       </c>
       <c r="I7" t="s">
@@ -2659,7 +2659,7 @@
       <c r="G8">
         <v>6</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="8">
         <v>3</v>
       </c>
       <c r="I8" t="s">
@@ -2700,7 +2700,7 @@
       <c r="G9">
         <v>11</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="8">
         <v>11</v>
       </c>
       <c r="I9" t="s">
@@ -2741,7 +2741,7 @@
       <c r="G10">
         <v>7</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="8">
         <v>13</v>
       </c>
       <c r="I10" t="s">
@@ -2782,7 +2782,7 @@
       <c r="G11">
         <v>8</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="8">
         <v>22</v>
       </c>
       <c r="I11" t="s">
@@ -2823,7 +2823,7 @@
       <c r="G12">
         <v>12</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="8">
         <v>12</v>
       </c>
       <c r="I12" t="s">
@@ -2864,7 +2864,7 @@
       <c r="G13">
         <v>20</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="8">
         <v>6</v>
       </c>
       <c r="I13" t="s">
@@ -2905,7 +2905,7 @@
       <c r="G14">
         <v>13</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="8">
         <v>15</v>
       </c>
       <c r="I14" t="s">
@@ -2946,7 +2946,7 @@
       <c r="G15">
         <v>14</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="8">
         <v>16</v>
       </c>
       <c r="I15" t="s">
@@ -2987,7 +2987,7 @@
       <c r="G16">
         <v>21</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="8">
         <v>18</v>
       </c>
       <c r="I16" t="s">
@@ -3028,7 +3028,7 @@
       <c r="G17">
         <v>15</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="8">
         <v>9</v>
       </c>
       <c r="I17" t="s">
@@ -3069,7 +3069,7 @@
       <c r="G18">
         <v>22</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="8">
         <v>10</v>
       </c>
       <c r="I18" t="s">
@@ -3110,7 +3110,7 @@
       <c r="G19">
         <v>9</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="8">
         <v>8</v>
       </c>
       <c r="I19" t="s">
@@ -3151,7 +3151,7 @@
       <c r="G20">
         <v>16</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="8">
         <v>24</v>
       </c>
       <c r="I20" t="s">
@@ -3192,7 +3192,7 @@
       <c r="G21">
         <v>23</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="8">
         <v>19</v>
       </c>
       <c r="I21" t="s">
@@ -3233,7 +3233,7 @@
       <c r="G22">
         <v>17</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="8">
         <v>20</v>
       </c>
       <c r="I22" t="s">
@@ -3274,7 +3274,7 @@
       <c r="G23">
         <v>18</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="8">
         <v>14</v>
       </c>
       <c r="I23" t="s">
@@ -3315,7 +3315,7 @@
       <c r="G24">
         <v>24</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="8">
         <v>17</v>
       </c>
       <c r="I24" t="s">
@@ -3356,7 +3356,7 @@
       <c r="G25">
         <v>19</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="8">
         <v>25</v>
       </c>
       <c r="I25" t="s">
@@ -3397,7 +3397,7 @@
       <c r="G26">
         <v>25</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="8">
         <v>21</v>
       </c>
       <c r="I26" t="s">
@@ -3438,7 +3438,7 @@
       <c r="G27">
         <v>1</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="8">
         <v>8</v>
       </c>
       <c r="I27" t="s">
@@ -3479,7 +3479,7 @@
       <c r="G28">
         <v>8</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="8">
         <v>24</v>
       </c>
       <c r="I28" t="s">
@@ -3520,7 +3520,7 @@
       <c r="G29">
         <v>2</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="8">
         <v>7</v>
       </c>
       <c r="I29" t="s">
@@ -3561,7 +3561,7 @@
       <c r="G30">
         <v>3</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="8">
         <v>1</v>
       </c>
       <c r="I30" t="s">
@@ -3602,7 +3602,7 @@
       <c r="G31">
         <v>4</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="8">
         <v>4</v>
       </c>
       <c r="I31" t="s">
@@ -3643,7 +3643,7 @@
       <c r="G32">
         <v>5</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="8">
         <v>3</v>
       </c>
       <c r="I32" t="s">
@@ -3684,7 +3684,7 @@
       <c r="G33">
         <v>10</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="8">
         <v>6</v>
       </c>
       <c r="I33" t="s">
@@ -3725,7 +3725,7 @@
       <c r="G34">
         <v>11</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="8">
         <v>5</v>
       </c>
       <c r="I34" t="s">
@@ -3766,7 +3766,7 @@
       <c r="G35">
         <v>21</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="8">
         <v>13</v>
       </c>
       <c r="I35" t="s">
@@ -3807,7 +3807,7 @@
       <c r="G36">
         <v>12</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="8">
         <v>2</v>
       </c>
       <c r="I36" t="s">
@@ -3848,7 +3848,7 @@
       <c r="G37">
         <v>6</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="8">
         <v>14</v>
       </c>
       <c r="I37" t="s">
@@ -3889,7 +3889,7 @@
       <c r="G38">
         <v>7</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="8">
         <v>16</v>
       </c>
       <c r="I38" t="s">
@@ -3930,7 +3930,7 @@
       <c r="G39">
         <v>13</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="8">
         <v>10</v>
       </c>
       <c r="I39" t="s">
@@ -3971,7 +3971,7 @@
       <c r="G40">
         <v>14</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="8">
         <v>12</v>
       </c>
       <c r="I40" t="s">
@@ -4012,7 +4012,7 @@
       <c r="G41">
         <v>15</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="8">
         <v>11</v>
       </c>
       <c r="I41" t="s">
@@ -4053,7 +4053,7 @@
       <c r="G42">
         <v>16</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="8">
         <v>22</v>
       </c>
       <c r="I42" t="s">
@@ -4094,7 +4094,7 @@
       <c r="G43">
         <v>17</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="8">
         <v>17</v>
       </c>
       <c r="I43" t="s">
@@ -4135,7 +4135,7 @@
       <c r="G44">
         <v>18</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="8">
         <v>9</v>
       </c>
       <c r="I44" t="s">
@@ -4176,7 +4176,7 @@
       <c r="G45">
         <v>22</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="8">
         <v>20</v>
       </c>
       <c r="I45" t="s">
@@ -4217,7 +4217,7 @@
       <c r="G46">
         <v>19</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="8">
         <v>23</v>
       </c>
       <c r="I46" t="s">
@@ -4258,7 +4258,7 @@
       <c r="G47">
         <v>9</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="8">
         <v>25</v>
       </c>
       <c r="I47" t="s">
@@ -4299,7 +4299,7 @@
       <c r="G48">
         <v>23</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="8">
         <v>19</v>
       </c>
       <c r="I48" t="s">
@@ -4340,7 +4340,7 @@
       <c r="G49">
         <v>20</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="8">
         <v>15</v>
       </c>
       <c r="I49" t="s">
@@ -4381,7 +4381,7 @@
       <c r="G50">
         <v>24</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="8">
         <v>18</v>
       </c>
       <c r="I50" t="s">
@@ -4422,7 +4422,7 @@
       <c r="G51">
         <v>25</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="8">
         <v>21</v>
       </c>
       <c r="I51" t="s">
@@ -4463,7 +4463,7 @@
       <c r="G52">
         <v>1</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="8">
         <v>5</v>
       </c>
       <c r="I52" t="s">
@@ -4506,7 +4506,7 @@
       <c r="G53">
         <v>2</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="8">
         <v>2</v>
       </c>
       <c r="I53" t="s">
@@ -4548,7 +4548,7 @@
       <c r="G54">
         <v>3</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="8">
         <v>8</v>
       </c>
       <c r="I54" t="s">
@@ -4590,7 +4590,7 @@
       <c r="G55">
         <v>4</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="8">
         <v>11</v>
       </c>
       <c r="I55" t="s">
@@ -4632,7 +4632,7 @@
       <c r="G56">
         <v>5</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="8">
         <v>7</v>
       </c>
       <c r="I56" t="s">
@@ -4674,7 +4674,7 @@
       <c r="G57">
         <v>11</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="8">
         <v>15</v>
       </c>
       <c r="I57" t="s">
@@ -4716,7 +4716,7 @@
       <c r="G58">
         <v>6</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="8">
         <v>6</v>
       </c>
       <c r="I58" t="s">
@@ -4758,7 +4758,7 @@
       <c r="G59">
         <v>12</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="8">
         <v>10</v>
       </c>
       <c r="I59" t="s">
@@ -4800,7 +4800,7 @@
       <c r="G60">
         <v>20</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="8">
         <v>25</v>
       </c>
       <c r="I60" t="s">
@@ -4842,7 +4842,7 @@
       <c r="G61">
         <v>7</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="8">
         <v>1</v>
       </c>
       <c r="I61" t="s">
@@ -4884,7 +4884,7 @@
       <c r="G62">
         <v>8</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="8">
         <v>3</v>
       </c>
       <c r="I62" t="s">
@@ -4926,7 +4926,7 @@
       <c r="G63">
         <v>13</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="8">
         <v>9</v>
       </c>
       <c r="I63" t="s">
@@ -4968,7 +4968,7 @@
       <c r="G64">
         <v>14</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="8">
         <v>17</v>
       </c>
       <c r="I64" t="s">
@@ -5010,7 +5010,7 @@
       <c r="G65">
         <v>9</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="8">
         <v>20</v>
       </c>
       <c r="I65" t="s">
@@ -5052,7 +5052,7 @@
       <c r="G66">
         <v>15</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="8">
         <v>4</v>
       </c>
       <c r="I66" t="s">
@@ -5094,7 +5094,7 @@
       <c r="G67">
         <v>21</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="8">
         <v>12</v>
       </c>
       <c r="I67" t="s">
@@ -5136,7 +5136,7 @@
       <c r="G68">
         <v>22</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="8">
         <v>22</v>
       </c>
       <c r="I68" t="s">
@@ -5178,7 +5178,7 @@
       <c r="G69">
         <v>16</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="8">
         <v>14</v>
       </c>
       <c r="I69" t="s">
@@ -5220,7 +5220,7 @@
       <c r="G70">
         <v>23</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="8">
         <v>16</v>
       </c>
       <c r="I70" t="s">
@@ -5262,7 +5262,7 @@
       <c r="G71">
         <v>17</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="8">
         <v>18</v>
       </c>
       <c r="I71" t="s">
@@ -5304,7 +5304,7 @@
       <c r="G72">
         <v>10</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="8">
         <v>19</v>
       </c>
       <c r="I72" t="s">
@@ -5346,7 +5346,7 @@
       <c r="G73">
         <v>18</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="8">
         <v>23</v>
       </c>
       <c r="I73" t="s">
@@ -5388,7 +5388,7 @@
       <c r="G74">
         <v>19</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="8">
         <v>13</v>
       </c>
       <c r="I74" t="s">
@@ -5430,7 +5430,7 @@
       <c r="G75">
         <v>24</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="8">
         <v>24</v>
       </c>
       <c r="I75" t="s">
@@ -5472,7 +5472,7 @@
       <c r="G76">
         <v>25</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="8">
         <v>21</v>
       </c>
       <c r="I76" t="s">
@@ -5514,6 +5514,9 @@
       <c r="G77">
         <v>1</v>
       </c>
+      <c r="H77" s="8">
+        <v>1</v>
+      </c>
       <c r="I77" t="s">
         <v>75</v>
       </c>
@@ -5551,6 +5554,9 @@
       <c r="G78">
         <v>7</v>
       </c>
+      <c r="H78" s="8">
+        <v>16</v>
+      </c>
       <c r="I78" t="s">
         <v>75</v>
       </c>
@@ -5588,6 +5594,9 @@
       <c r="G79">
         <v>8</v>
       </c>
+      <c r="H79" s="8">
+        <v>7</v>
+      </c>
       <c r="I79" t="s">
         <v>75</v>
       </c>
@@ -5625,6 +5634,9 @@
       <c r="G80">
         <v>9</v>
       </c>
+      <c r="H80" s="8">
+        <v>10</v>
+      </c>
       <c r="I80" t="s">
         <v>75</v>
       </c>
@@ -5662,6 +5674,9 @@
       <c r="G81">
         <v>3</v>
       </c>
+      <c r="H81" s="8">
+        <v>2</v>
+      </c>
       <c r="I81" t="s">
         <v>75</v>
       </c>
@@ -5699,6 +5714,9 @@
       <c r="G82">
         <v>2</v>
       </c>
+      <c r="H82" s="8">
+        <v>17</v>
+      </c>
       <c r="I82" t="s">
         <v>75</v>
       </c>
@@ -5736,6 +5754,9 @@
       <c r="G83">
         <v>10</v>
       </c>
+      <c r="H83" s="8">
+        <v>6</v>
+      </c>
       <c r="I83" t="s">
         <v>75</v>
       </c>
@@ -5773,6 +5794,9 @@
       <c r="G84">
         <v>4</v>
       </c>
+      <c r="H84" s="8">
+        <v>5</v>
+      </c>
       <c r="I84" t="s">
         <v>75</v>
       </c>
@@ -5810,6 +5834,9 @@
       <c r="G85">
         <v>5</v>
       </c>
+      <c r="H85" s="8">
+        <v>12</v>
+      </c>
       <c r="I85" t="s">
         <v>75</v>
       </c>
@@ -5847,6 +5874,9 @@
       <c r="G86">
         <v>11</v>
       </c>
+      <c r="H86" s="8">
+        <v>11</v>
+      </c>
       <c r="I86" t="s">
         <v>75</v>
       </c>
@@ -5884,6 +5914,9 @@
       <c r="G87">
         <v>6</v>
       </c>
+      <c r="H87" s="8">
+        <v>4</v>
+      </c>
       <c r="I87" t="s">
         <v>75</v>
       </c>
@@ -5921,6 +5954,9 @@
       <c r="G88">
         <v>12</v>
       </c>
+      <c r="H88" s="8">
+        <v>13</v>
+      </c>
       <c r="I88" t="s">
         <v>75</v>
       </c>
@@ -5958,6 +5994,9 @@
       <c r="G89">
         <v>13</v>
       </c>
+      <c r="H89" s="8">
+        <v>9</v>
+      </c>
       <c r="I89" t="s">
         <v>75</v>
       </c>
@@ -5995,6 +6034,9 @@
       <c r="G90">
         <v>20</v>
       </c>
+      <c r="H90" s="8">
+        <v>3</v>
+      </c>
       <c r="I90" t="s">
         <v>75</v>
       </c>
@@ -6032,6 +6074,9 @@
       <c r="G91">
         <v>14</v>
       </c>
+      <c r="H91" s="8">
+        <v>20</v>
+      </c>
       <c r="I91" t="s">
         <v>75</v>
       </c>
@@ -6069,6 +6114,9 @@
       <c r="G92">
         <v>15</v>
       </c>
+      <c r="H92" s="8">
+        <v>15</v>
+      </c>
       <c r="I92" t="s">
         <v>75</v>
       </c>
@@ -6106,6 +6154,9 @@
       <c r="G93">
         <v>16</v>
       </c>
+      <c r="H93" s="8">
+        <v>14</v>
+      </c>
       <c r="I93" t="s">
         <v>75</v>
       </c>
@@ -6143,6 +6194,9 @@
       <c r="G94">
         <v>21</v>
       </c>
+      <c r="H94" s="8">
+        <v>18</v>
+      </c>
       <c r="I94" t="s">
         <v>75</v>
       </c>
@@ -6180,6 +6234,9 @@
       <c r="G95">
         <v>22</v>
       </c>
+      <c r="H95" s="8">
+        <v>19</v>
+      </c>
       <c r="I95" t="s">
         <v>75</v>
       </c>
@@ -6217,6 +6274,9 @@
       <c r="G96">
         <v>17</v>
       </c>
+      <c r="H96" s="8">
+        <v>8</v>
+      </c>
       <c r="I96" t="s">
         <v>75</v>
       </c>
@@ -6254,6 +6314,9 @@
       <c r="G97">
         <v>18</v>
       </c>
+      <c r="H97" s="8">
+        <v>25</v>
+      </c>
       <c r="I97" t="s">
         <v>75</v>
       </c>
@@ -6291,6 +6354,9 @@
       <c r="G98">
         <v>23</v>
       </c>
+      <c r="H98" s="8">
+        <v>24</v>
+      </c>
       <c r="I98" t="s">
         <v>75</v>
       </c>
@@ -6328,6 +6394,9 @@
       <c r="G99">
         <v>19</v>
       </c>
+      <c r="H99" s="8">
+        <v>23</v>
+      </c>
       <c r="I99" t="s">
         <v>75</v>
       </c>
@@ -6365,6 +6434,9 @@
       <c r="G100">
         <v>24</v>
       </c>
+      <c r="H100" s="8">
+        <v>21</v>
+      </c>
       <c r="I100" t="s">
         <v>75</v>
       </c>
@@ -6402,6 +6474,9 @@
       <c r="G101">
         <v>25</v>
       </c>
+      <c r="H101" s="8">
+        <v>22</v>
+      </c>
       <c r="I101" t="s">
         <v>75</v>
       </c>
@@ -6414,6 +6489,774 @@
       <c r="L101">
         <v>5.56</v>
       </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H102" s="8"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H103" s="8"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H104" s="8"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H105" s="8"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H106" s="8"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H107" s="8"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H108" s="8"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H109" s="8"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H110" s="8"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H111" s="8"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="H112" s="8"/>
+    </row>
+    <row r="113" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H113" s="8"/>
+    </row>
+    <row r="114" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H114" s="8"/>
+    </row>
+    <row r="115" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H115" s="8"/>
+    </row>
+    <row r="116" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H116" s="8"/>
+    </row>
+    <row r="117" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H117" s="8"/>
+    </row>
+    <row r="118" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H118" s="8"/>
+    </row>
+    <row r="119" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H119" s="8"/>
+    </row>
+    <row r="120" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H120" s="8"/>
+    </row>
+    <row r="121" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H121" s="8"/>
+    </row>
+    <row r="122" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H122" s="8"/>
+    </row>
+    <row r="123" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H123" s="8"/>
+    </row>
+    <row r="124" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H124" s="8"/>
+    </row>
+    <row r="125" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H125" s="8"/>
+    </row>
+    <row r="126" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H126" s="8"/>
+    </row>
+    <row r="127" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H127" s="8"/>
+    </row>
+    <row r="128" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H128" s="8"/>
+    </row>
+    <row r="129" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H129" s="8"/>
+    </row>
+    <row r="130" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H130" s="8"/>
+    </row>
+    <row r="131" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H131" s="8"/>
+    </row>
+    <row r="132" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H132" s="8"/>
+    </row>
+    <row r="133" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H133" s="8"/>
+    </row>
+    <row r="134" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H134" s="8"/>
+    </row>
+    <row r="135" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H135" s="8"/>
+    </row>
+    <row r="136" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H136" s="8"/>
+    </row>
+    <row r="137" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H137" s="8"/>
+    </row>
+    <row r="138" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H138" s="8"/>
+    </row>
+    <row r="139" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H139" s="8"/>
+    </row>
+    <row r="140" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H140" s="8"/>
+    </row>
+    <row r="141" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H141" s="8"/>
+    </row>
+    <row r="142" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H142" s="8"/>
+    </row>
+    <row r="143" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H143" s="8"/>
+    </row>
+    <row r="144" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H144" s="8"/>
+    </row>
+    <row r="145" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H145" s="8"/>
+    </row>
+    <row r="146" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H146" s="8"/>
+    </row>
+    <row r="147" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H147" s="8"/>
+    </row>
+    <row r="148" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H148" s="8"/>
+    </row>
+    <row r="149" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H149" s="8"/>
+    </row>
+    <row r="150" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H150" s="8"/>
+    </row>
+    <row r="151" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H151" s="8"/>
+    </row>
+    <row r="152" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H152" s="8"/>
+    </row>
+    <row r="153" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H153" s="8"/>
+    </row>
+    <row r="154" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H154" s="8"/>
+    </row>
+    <row r="155" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H155" s="8"/>
+    </row>
+    <row r="156" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H156" s="8"/>
+    </row>
+    <row r="157" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H157" s="8"/>
+    </row>
+    <row r="158" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H158" s="8"/>
+    </row>
+    <row r="159" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H159" s="8"/>
+    </row>
+    <row r="160" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H160" s="8"/>
+    </row>
+    <row r="161" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H161" s="8"/>
+    </row>
+    <row r="162" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H162" s="8"/>
+    </row>
+    <row r="163" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H163" s="8"/>
+    </row>
+    <row r="164" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H164" s="8"/>
+    </row>
+    <row r="165" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H165" s="8"/>
+    </row>
+    <row r="166" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H166" s="8"/>
+    </row>
+    <row r="167" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H167" s="8"/>
+    </row>
+    <row r="168" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H168" s="8"/>
+    </row>
+    <row r="169" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H169" s="8"/>
+    </row>
+    <row r="170" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H170" s="8"/>
+    </row>
+    <row r="171" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H171" s="8"/>
+    </row>
+    <row r="172" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H172" s="8"/>
+    </row>
+    <row r="173" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H173" s="8"/>
+    </row>
+    <row r="174" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H174" s="8"/>
+    </row>
+    <row r="175" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H175" s="8"/>
+    </row>
+    <row r="176" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H176" s="8"/>
+    </row>
+    <row r="177" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H177" s="8"/>
+    </row>
+    <row r="178" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H178" s="8"/>
+    </row>
+    <row r="179" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H179" s="8"/>
+    </row>
+    <row r="180" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H180" s="8"/>
+    </row>
+    <row r="181" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H181" s="8"/>
+    </row>
+    <row r="182" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H182" s="8"/>
+    </row>
+    <row r="183" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H183" s="8"/>
+    </row>
+    <row r="184" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H184" s="8"/>
+    </row>
+    <row r="185" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H185" s="8"/>
+    </row>
+    <row r="186" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H186" s="8"/>
+    </row>
+    <row r="187" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H187" s="8"/>
+    </row>
+    <row r="188" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H188" s="8"/>
+    </row>
+    <row r="189" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H189" s="8"/>
+    </row>
+    <row r="190" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H190" s="8"/>
+    </row>
+    <row r="191" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H191" s="8"/>
+    </row>
+    <row r="192" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H192" s="8"/>
+    </row>
+    <row r="193" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H193" s="8"/>
+    </row>
+    <row r="194" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H194" s="8"/>
+    </row>
+    <row r="195" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H195" s="8"/>
+    </row>
+    <row r="196" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H196" s="8"/>
+    </row>
+    <row r="197" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H197" s="8"/>
+    </row>
+    <row r="198" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H198" s="8"/>
+    </row>
+    <row r="199" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H199" s="8"/>
+    </row>
+    <row r="200" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H200" s="8"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H201" s="8"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H202" s="8"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H203" s="8"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H204" s="8"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H205" s="8"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H206" s="8"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H207" s="8"/>
+    </row>
+    <row r="208" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H208" s="8"/>
+    </row>
+    <row r="209" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H209" s="8"/>
+    </row>
+    <row r="210" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H210" s="8"/>
+    </row>
+    <row r="211" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H211" s="8"/>
+    </row>
+    <row r="212" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H212" s="8"/>
+    </row>
+    <row r="213" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H213" s="8"/>
+    </row>
+    <row r="214" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H214" s="8"/>
+    </row>
+    <row r="215" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H215" s="8"/>
+    </row>
+    <row r="216" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H216" s="8"/>
+    </row>
+    <row r="217" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H217" s="8"/>
+    </row>
+    <row r="218" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H218" s="8"/>
+    </row>
+    <row r="219" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H219" s="8"/>
+    </row>
+    <row r="220" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H220" s="8"/>
+    </row>
+    <row r="221" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H221" s="8"/>
+    </row>
+    <row r="222" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H222" s="8"/>
+    </row>
+    <row r="223" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H223" s="8"/>
+    </row>
+    <row r="224" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H224" s="8"/>
+    </row>
+    <row r="225" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H225" s="8"/>
+    </row>
+    <row r="226" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H226" s="8"/>
+    </row>
+    <row r="227" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H227" s="8"/>
+    </row>
+    <row r="228" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H228" s="8"/>
+    </row>
+    <row r="229" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H229" s="8"/>
+    </row>
+    <row r="230" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H230" s="8"/>
+    </row>
+    <row r="231" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H231" s="8"/>
+    </row>
+    <row r="232" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H232" s="8"/>
+    </row>
+    <row r="233" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H233" s="8"/>
+    </row>
+    <row r="234" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H234" s="8"/>
+    </row>
+    <row r="235" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H235" s="8"/>
+    </row>
+    <row r="236" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H236" s="8"/>
+    </row>
+    <row r="237" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H237" s="8"/>
+    </row>
+    <row r="238" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H238" s="8"/>
+    </row>
+    <row r="239" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H239" s="8"/>
+    </row>
+    <row r="240" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H240" s="8"/>
+    </row>
+    <row r="241" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H241" s="8"/>
+    </row>
+    <row r="242" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H242" s="8"/>
+    </row>
+    <row r="243" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H243" s="8"/>
+    </row>
+    <row r="244" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H244" s="8"/>
+    </row>
+    <row r="245" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H245" s="8"/>
+    </row>
+    <row r="246" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H246" s="8"/>
+    </row>
+    <row r="247" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H247" s="8"/>
+    </row>
+    <row r="248" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H248" s="8"/>
+    </row>
+    <row r="249" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H249" s="8"/>
+    </row>
+    <row r="250" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H250" s="8"/>
+    </row>
+    <row r="251" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H251" s="8"/>
+    </row>
+    <row r="252" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H252" s="8"/>
+    </row>
+    <row r="253" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H253" s="8"/>
+    </row>
+    <row r="254" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H254" s="8"/>
+    </row>
+    <row r="255" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H255" s="8"/>
+    </row>
+    <row r="256" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H256" s="8"/>
+    </row>
+    <row r="257" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H257" s="8"/>
+    </row>
+    <row r="258" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H258" s="8"/>
+    </row>
+    <row r="259" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H259" s="8"/>
+    </row>
+    <row r="260" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H260" s="8"/>
+    </row>
+    <row r="261" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H261" s="8"/>
+    </row>
+    <row r="262" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H262" s="8"/>
+    </row>
+    <row r="263" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H263" s="8"/>
+    </row>
+    <row r="264" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H264" s="8"/>
+    </row>
+    <row r="265" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H265" s="8"/>
+    </row>
+    <row r="266" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H266" s="8"/>
+    </row>
+    <row r="267" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H267" s="8"/>
+    </row>
+    <row r="268" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H268" s="8"/>
+    </row>
+    <row r="269" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H269" s="8"/>
+    </row>
+    <row r="270" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H270" s="8"/>
+    </row>
+    <row r="271" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H271" s="8"/>
+    </row>
+    <row r="272" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H272" s="8"/>
+    </row>
+    <row r="273" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H273" s="8"/>
+    </row>
+    <row r="274" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H274" s="8"/>
+    </row>
+    <row r="275" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H275" s="8"/>
+    </row>
+    <row r="276" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H276" s="8"/>
+    </row>
+    <row r="277" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H277" s="8"/>
+    </row>
+    <row r="278" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H278" s="8"/>
+    </row>
+    <row r="279" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H279" s="8"/>
+    </row>
+    <row r="280" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H280" s="8"/>
+    </row>
+    <row r="281" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H281" s="8"/>
+    </row>
+    <row r="282" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H282" s="8"/>
+    </row>
+    <row r="283" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H283" s="8"/>
+    </row>
+    <row r="284" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H284" s="8"/>
+    </row>
+    <row r="285" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H285" s="8"/>
+    </row>
+    <row r="286" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H286" s="8"/>
+    </row>
+    <row r="287" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H287" s="8"/>
+    </row>
+    <row r="288" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H288" s="8"/>
+    </row>
+    <row r="289" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H289" s="8"/>
+    </row>
+    <row r="290" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H290" s="8"/>
+    </row>
+    <row r="291" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H291" s="8"/>
+    </row>
+    <row r="292" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H292" s="8"/>
+    </row>
+    <row r="293" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H293" s="8"/>
+    </row>
+    <row r="294" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H294" s="8"/>
+    </row>
+    <row r="295" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H295" s="8"/>
+    </row>
+    <row r="296" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H296" s="8"/>
+    </row>
+    <row r="297" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H297" s="8"/>
+    </row>
+    <row r="298" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H298" s="8"/>
+    </row>
+    <row r="299" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H299" s="8"/>
+    </row>
+    <row r="300" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H300" s="8"/>
+    </row>
+    <row r="301" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H301" s="8"/>
+    </row>
+    <row r="302" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H302" s="8"/>
+    </row>
+    <row r="303" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H303" s="8"/>
+    </row>
+    <row r="304" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H304" s="8"/>
+    </row>
+    <row r="305" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H305" s="8"/>
+    </row>
+    <row r="306" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H306" s="8"/>
+    </row>
+    <row r="307" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H307" s="8"/>
+    </row>
+    <row r="308" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H308" s="8"/>
+    </row>
+    <row r="309" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H309" s="8"/>
+    </row>
+    <row r="310" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H310" s="8"/>
+    </row>
+    <row r="311" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H311" s="8"/>
+    </row>
+    <row r="312" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H312" s="8"/>
+    </row>
+    <row r="313" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H313" s="8"/>
+    </row>
+    <row r="314" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H314" s="8"/>
+    </row>
+    <row r="315" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H315" s="8"/>
+    </row>
+    <row r="316" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H316" s="8"/>
+    </row>
+    <row r="317" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H317" s="8"/>
+    </row>
+    <row r="318" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H318" s="8"/>
+    </row>
+    <row r="319" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H319" s="8"/>
+    </row>
+    <row r="320" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H320" s="8"/>
+    </row>
+    <row r="321" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H321" s="8"/>
+    </row>
+    <row r="322" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H322" s="8"/>
+    </row>
+    <row r="323" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H323" s="8"/>
+    </row>
+    <row r="324" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H324" s="8"/>
+    </row>
+    <row r="325" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H325" s="8"/>
+    </row>
+    <row r="326" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H326" s="8"/>
+    </row>
+    <row r="327" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H327" s="8"/>
+    </row>
+    <row r="328" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H328" s="8"/>
+    </row>
+    <row r="329" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H329" s="8"/>
+    </row>
+    <row r="330" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H330" s="8"/>
+    </row>
+    <row r="331" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H331" s="8"/>
+    </row>
+    <row r="332" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H332" s="8"/>
+    </row>
+    <row r="333" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H333" s="8"/>
+    </row>
+    <row r="334" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H334" s="8"/>
+    </row>
+    <row r="335" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H335" s="8"/>
+    </row>
+    <row r="336" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H336" s="8"/>
+    </row>
+    <row r="337" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H337" s="8"/>
+    </row>
+    <row r="338" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H338" s="8"/>
+    </row>
+    <row r="339" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H339" s="8"/>
+    </row>
+    <row r="340" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H340" s="8"/>
+    </row>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H341" s="8"/>
+    </row>
+    <row r="342" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H342" s="8"/>
+    </row>
+    <row r="343" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H343" s="8"/>
+    </row>
+    <row r="344" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H344" s="8"/>
+    </row>
+    <row r="345" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H345" s="8"/>
+    </row>
+    <row r="346" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H346" s="8"/>
+    </row>
+    <row r="347" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H347" s="8"/>
+    </row>
+    <row r="348" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H348" s="8"/>
+    </row>
+    <row r="349" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H349" s="8"/>
+    </row>
+    <row r="350" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H350" s="8"/>
+    </row>
+    <row r="351" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H351" s="8"/>
+    </row>
+    <row r="352" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H352" s="8"/>
+    </row>
+    <row r="353" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H353" s="8"/>
+    </row>
+    <row r="354" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H354" s="8"/>
+    </row>
+    <row r="355" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H355" s="8"/>
+    </row>
+    <row r="356" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H356" s="8"/>
+    </row>
+    <row r="357" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="H357" s="8"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N28:O52">

--- a/predictions/model_compare.xlsx
+++ b/predictions/model_compare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ripa_\Desktop\Programing\IndyCar_Project\predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B42EB2C-9579-43C0-B0C1-CA365EA78B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15710D4E-8550-4885-81AE-A346F055808B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{74EB7EE7-EB5C-4423-87E4-FE46F1C4926A}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" firstSheet="2" activeTab="2" xr2:uid="{74EB7EE7-EB5C-4423-87E4-FE46F1C4926A}"/>
   </bookViews>
   <sheets>
     <sheet name="Pre-Qualy_Model" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="89">
   <si>
     <t>Model</t>
   </si>
@@ -304,6 +304,12 @@
   <si>
     <t>Post-Qualy</t>
   </si>
+  <si>
+    <t>XGB</t>
+  </si>
+  <si>
+    <t>Streets of Long Beach</t>
+  </si>
 </sst>
 </file>
 
@@ -410,17 +416,17 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -932,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF436913-6699-4642-91DA-EC5EA358EA79}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.3671875" bestFit="1" customWidth="1"/>
@@ -943,22 +949,22 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11" t="s">
+      <c r="G1" s="13"/>
+      <c r="H1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="11"/>
+      <c r="I1" s="13"/>
       <c r="J1" t="s">
         <v>51</v>
       </c>
@@ -992,614 +998,690 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="B3" s="1">
-        <v>0.24360000000000001</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="C3" s="1">
-        <v>8.5199999999999998E-2</v>
+        <v>3.5400000000000001E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>0.23630000000000001</v>
+        <v>0.2576</v>
       </c>
       <c r="E3" s="1">
-        <v>0.1368</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="F3" s="1">
-        <v>0.216</v>
+        <v>0.2208</v>
       </c>
       <c r="G3" s="1">
-        <v>0.25130000000000002</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>0.22289999999999999</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="I3" s="1">
-        <v>0.18629999999999999</v>
+        <v>0.13220000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>0.24390000000000001</v>
+        <v>0.2427</v>
       </c>
       <c r="C4" s="1">
-        <v>6.1199999999999997E-2</v>
+        <v>9.0700000000000003E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>0.24079999999999999</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="E4" s="1">
-        <v>0.1162</v>
+        <v>0.13930000000000001</v>
       </c>
       <c r="F4" s="1">
-        <v>0.2203</v>
+        <v>0.21579999999999999</v>
       </c>
       <c r="G4" s="1">
-        <v>0.2185</v>
+        <v>0.251</v>
       </c>
       <c r="H4" s="1">
-        <v>0.23080000000000001</v>
+        <v>0.22170000000000001</v>
       </c>
       <c r="I4" s="1">
-        <v>0.1535</v>
+        <v>0.2039</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>0.24610000000000001</v>
+        <v>0.24329999999999999</v>
       </c>
       <c r="C5" s="1">
-        <v>4.1700000000000001E-2</v>
+        <v>6.83E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>0.23710000000000001</v>
+        <v>0.24079999999999999</v>
       </c>
       <c r="E5" s="1">
-        <v>0.1231</v>
+        <v>0.1186</v>
       </c>
       <c r="F5" s="1">
-        <v>0.2132</v>
+        <v>0.22370000000000001</v>
       </c>
       <c r="G5" s="1">
-        <v>0.25729999999999997</v>
+        <v>0.22170000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>0.22270000000000001</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="I5" s="1">
-        <v>0.1736</v>
+        <v>0.1794</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>0.24840000000000001</v>
+        <v>0.24610000000000001</v>
       </c>
       <c r="C6" s="1">
-        <v>9.2999999999999992E-3</v>
+        <v>4.9500000000000002E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>0.23580000000000001</v>
+        <v>0.23760000000000001</v>
       </c>
       <c r="E6" s="1">
-        <v>0.13769999999999999</v>
+        <v>0.12139999999999999</v>
       </c>
       <c r="F6" s="1">
-        <v>0.21249999999999999</v>
+        <v>0.2137</v>
       </c>
       <c r="G6" s="1">
-        <v>0.25979999999999998</v>
+        <v>0.25030000000000002</v>
       </c>
       <c r="H6" s="1">
-        <v>0.22120000000000001</v>
+        <v>0.21840000000000001</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1797</v>
+        <v>0.19309999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>0.23569999999999999</v>
+        <v>0.2477</v>
       </c>
       <c r="C7" s="1">
-        <v>0.14050000000000001</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>0.23569999999999999</v>
+        <v>0.2364</v>
       </c>
       <c r="E7" s="1">
-        <v>0.14050000000000001</v>
+        <v>0.13469999999999999</v>
       </c>
       <c r="F7" s="1">
-        <v>0.21410000000000001</v>
+        <v>0.2147</v>
       </c>
       <c r="G7" s="1">
-        <v>0.25740000000000002</v>
+        <v>0.25440000000000002</v>
       </c>
       <c r="H7" s="1">
-        <v>0.22189999999999999</v>
+        <v>0.22020000000000001</v>
       </c>
       <c r="I7" s="1">
-        <v>0.18229999999999999</v>
+        <v>0.1993</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1">
-        <v>0.2369</v>
+        <v>0.23580000000000001</v>
       </c>
       <c r="C8" s="1">
-        <v>0.12870000000000001</v>
+        <v>0.14030000000000001</v>
       </c>
       <c r="D8" s="1">
-        <v>0.23619999999999999</v>
+        <v>0.23580000000000001</v>
       </c>
       <c r="E8" s="1">
-        <v>0.1351</v>
+        <v>0.14069999999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>0.21490000000000001</v>
+        <v>0.2152</v>
       </c>
       <c r="G8" s="1">
-        <v>0.25609999999999999</v>
+        <v>0.25369999999999998</v>
       </c>
       <c r="H8" s="1">
-        <v>0.22359999999999999</v>
+        <v>0.22109999999999999</v>
       </c>
       <c r="I8" s="1">
-        <v>0.17780000000000001</v>
+        <v>0.2036</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.23719999999999999</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.13639999999999999</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.2366</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.13830000000000001</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.2167</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.25030000000000002</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.22209999999999999</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.20039999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1">
-        <v>0.23680000000000001</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.13569999999999999</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.2361</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.13780000000000001</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.21410000000000001</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.25790000000000002</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0.22239999999999999</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0.18179999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="31.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="2" t="s">
+      <c r="B10" s="1">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.13550000000000001</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.23649999999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.13650000000000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.21510000000000001</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.25409999999999999</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.2203</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.2011</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="31.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="10" t="s">
+      <c r="C12" s="11"/>
+      <c r="D12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11" t="s">
+      <c r="E12" s="12"/>
+      <c r="F12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11" t="s">
+      <c r="G12" s="13"/>
+      <c r="H12" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" t="s">
+      <c r="I12" s="13"/>
+      <c r="J12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.24349999999999999</v>
-      </c>
-      <c r="C13" s="1">
-        <v>8.6300000000000002E-2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0.21629999999999999</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.25180000000000002</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0.22270000000000001</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0.19370000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="B14" s="1">
-        <v>0.2452</v>
+        <v>0.2475</v>
       </c>
       <c r="C14" s="1">
-        <v>5.1299999999999998E-2</v>
+        <v>3.8199999999999998E-2</v>
       </c>
       <c r="D14" s="1">
-        <v>0.24060000000000001</v>
+        <v>0.2576</v>
       </c>
       <c r="E14" s="1">
-        <v>0.121</v>
+        <v>2.2200000000000001E-2</v>
       </c>
       <c r="F14" s="1">
-        <v>0.21709999999999999</v>
+        <v>0.2248</v>
       </c>
       <c r="G14" s="1">
-        <v>0.23730000000000001</v>
+        <v>0.1782</v>
       </c>
       <c r="H14" s="1">
-        <v>0.2316</v>
+        <v>0.2321</v>
       </c>
       <c r="I14" s="1">
-        <v>0.1565</v>
+        <v>0.1192</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1">
-        <v>0.2475</v>
+        <v>0.24349999999999999</v>
       </c>
       <c r="C15" s="1">
-        <v>3.3799999999999997E-2</v>
+        <v>8.4599999999999995E-2</v>
       </c>
       <c r="D15" s="1">
-        <v>0.2366</v>
+        <v>0.2361</v>
       </c>
       <c r="E15" s="1">
-        <v>0.12559999999999999</v>
+        <v>0.13930000000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>0.2142</v>
+        <v>0.21659999999999999</v>
       </c>
       <c r="G15" s="1">
-        <v>0.25840000000000002</v>
+        <v>0.2492</v>
       </c>
       <c r="H15" s="1">
-        <v>0.22120000000000001</v>
+        <v>0.22140000000000001</v>
       </c>
       <c r="I15" s="1">
-        <v>0.18640000000000001</v>
+        <v>0.20899999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B16" s="1">
-        <v>0.24679999999999999</v>
+        <v>0.24379999999999999</v>
       </c>
       <c r="C16" s="1">
-        <v>2.1499999999999998E-2</v>
+        <v>6.1800000000000001E-2</v>
       </c>
       <c r="D16" s="1">
-        <v>0.23599999999999999</v>
+        <v>0.24030000000000001</v>
       </c>
       <c r="E16" s="1">
-        <v>0.1391</v>
+        <v>0.11940000000000001</v>
       </c>
       <c r="F16" s="1">
-        <v>0.21340000000000001</v>
+        <v>0.21870000000000001</v>
       </c>
       <c r="G16" s="1">
-        <v>0.2591</v>
+        <v>0.22989999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>0.22239999999999999</v>
+        <v>0.22739999999999999</v>
       </c>
       <c r="I16" s="1">
-        <v>0.17330000000000001</v>
+        <v>0.18379999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1">
-        <v>0.2356</v>
+        <v>0.24540000000000001</v>
       </c>
       <c r="C17" s="1">
-        <v>0.14219999999999999</v>
+        <v>4.8500000000000001E-2</v>
       </c>
       <c r="D17" s="1">
-        <v>0.2356</v>
+        <v>0.23619999999999999</v>
       </c>
       <c r="E17" s="1">
-        <v>0.14219999999999999</v>
+        <v>0.12959999999999999</v>
       </c>
       <c r="F17" s="1">
-        <v>0.2147</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25800000000000001</v>
+        <v>0.25569999999999998</v>
       </c>
       <c r="H17" s="1">
-        <v>0.2223</v>
+        <v>0.21859999999999999</v>
       </c>
       <c r="I17" s="1">
-        <v>0.18590000000000001</v>
+        <v>0.19789999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1">
-        <v>0.2356</v>
+        <v>0.24879999999999999</v>
       </c>
       <c r="C18" s="1">
-        <v>0.14019999999999999</v>
+        <v>-1.9E-3</v>
       </c>
       <c r="D18" s="1">
-        <v>0.2356</v>
+        <v>0.23580000000000001</v>
       </c>
       <c r="E18" s="1">
-        <v>0.1419</v>
+        <v>0.1399</v>
       </c>
       <c r="F18" s="1">
-        <v>0.21429999999999999</v>
+        <v>0.2142</v>
       </c>
       <c r="G18" s="1">
-        <v>0.25969999999999999</v>
+        <v>0.25230000000000002</v>
       </c>
       <c r="H18" s="1">
-        <v>0.22159999999999999</v>
+        <v>0.22040000000000001</v>
       </c>
       <c r="I18" s="1">
-        <v>0.1885</v>
+        <v>0.1983</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1">
-        <v>0.23699999999999999</v>
+        <v>0.2356</v>
       </c>
       <c r="C19" s="1">
-        <v>0.13880000000000001</v>
+        <v>0.1429</v>
       </c>
       <c r="D19" s="1">
-        <v>0.2364</v>
+        <v>0.2356</v>
       </c>
       <c r="E19" s="1">
-        <v>0.14050000000000001</v>
+        <v>0.14280000000000001</v>
       </c>
       <c r="F19" s="1">
-        <v>0.2165</v>
+        <v>0.2152</v>
       </c>
       <c r="G19" s="1">
-        <v>0.25290000000000001</v>
+        <v>0.25259999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>0.22370000000000001</v>
+        <v>0.22090000000000001</v>
       </c>
       <c r="I19" s="1">
-        <v>0.184</v>
+        <v>0.20549999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1">
-        <v>0.23649999999999999</v>
+        <v>0.2354</v>
       </c>
       <c r="C20" s="1">
-        <v>0.13869999999999999</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="D20" s="1">
-        <v>0.2359</v>
+        <v>0.23549999999999999</v>
       </c>
       <c r="E20" s="1">
-        <v>0.14030000000000001</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>0.21490000000000001</v>
+        <v>0.21429999999999999</v>
       </c>
       <c r="G20" s="1">
-        <v>0.25850000000000001</v>
+        <v>0.25559999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>0.22359999999999999</v>
+        <v>0.2205</v>
       </c>
       <c r="I20" s="1">
-        <v>0.1855</v>
+        <v>0.20569999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3" t="s">
-        <v>14</v>
+      <c r="A21" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B21" s="1">
-        <v>0.2359</v>
+        <v>0.23680000000000001</v>
       </c>
       <c r="C21" s="1">
-        <v>0.1366</v>
+        <v>0.1386</v>
       </c>
       <c r="D21" s="1">
-        <v>0.2359</v>
+        <v>0.23630000000000001</v>
       </c>
       <c r="E21" s="1">
-        <v>0.13900000000000001</v>
+        <v>0.14069999999999999</v>
       </c>
       <c r="F21" s="1">
-        <v>0.21490000000000001</v>
+        <v>0.21679999999999999</v>
       </c>
       <c r="G21" s="1">
-        <v>0.25750000000000001</v>
+        <v>0.24829999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>0.22220000000000001</v>
+        <v>0.222</v>
       </c>
       <c r="I21" s="1">
-        <v>0.19389999999999999</v>
+        <v>0.20369999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1">
-        <v>0.23569999999999999</v>
+        <v>0.23630000000000001</v>
       </c>
       <c r="C22" s="1">
-        <v>0.13769999999999999</v>
+        <v>0.13969999999999999</v>
       </c>
       <c r="D22" s="1">
         <v>0.23569999999999999</v>
       </c>
       <c r="E22" s="1">
-        <v>0.13980000000000001</v>
+        <v>0.1416</v>
       </c>
       <c r="F22" s="1">
-        <v>0.2135</v>
+        <v>0.21490000000000001</v>
       </c>
       <c r="G22" s="1">
-        <v>0.26169999999999999</v>
+        <v>0.254</v>
       </c>
       <c r="H22" s="1">
-        <v>0.2213</v>
+        <v>0.2205</v>
       </c>
       <c r="I22" s="1">
-        <v>0.18390000000000001</v>
+        <v>0.2039</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" t="s">
+      <c r="A23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.23569999999999999</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.1389</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.2359</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.14030000000000001</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.2145</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.25490000000000002</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0.20610000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0.23549999999999999</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.23549999999999999</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.21329999999999999</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.25690000000000002</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.21909999999999999</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0.2019</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" t="s">
         <v>62</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C25" t="s">
         <v>63</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D25" t="s">
         <v>64</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="D24" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="D26" t="s">
         <v>1</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E26" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="4">
-        <v>46085</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25">
-        <v>0.2293</v>
-      </c>
-      <c r="E25">
-        <v>0.13789999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="4">
-        <v>46090</v>
-      </c>
-      <c r="B26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26">
-        <v>0.223</v>
-      </c>
-      <c r="E26">
-        <v>0.1744</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27">
+        <v>0.2293</v>
+      </c>
+      <c r="E27">
+        <v>0.13789999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="4">
+        <v>46090</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>0.223</v>
+      </c>
+      <c r="E28">
+        <v>0.1744</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="4">
         <v>46098</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" t="s">
         <v>14</v>
       </c>
-      <c r="D27">
+      <c r="D29">
         <v>0.22220000000000001</v>
       </c>
-      <c r="E27">
+      <c r="E29">
         <v>0.19389999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="E29" s="5"/>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="4">
+        <v>46112</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="E30">
+        <v>0.20610000000000001</v>
+      </c>
+      <c r="G30" s="5">
+        <f>D30*25</f>
+        <v>5.4924999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="E31" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1607,58 +1689,58 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:B9">
-    <cfRule type="top10" dxfId="24" priority="45" bottom="1" rank="1"/>
+  <conditionalFormatting sqref="B3:B10">
+    <cfRule type="top10" dxfId="24" priority="57" bottom="1" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:B22">
-    <cfRule type="top10" dxfId="23" priority="87" bottom="1" rank="1"/>
+  <conditionalFormatting sqref="B14:B24">
+    <cfRule type="top10" dxfId="23" priority="99" bottom="1" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C9">
-    <cfRule type="top10" dxfId="22" priority="44" rank="1"/>
+  <conditionalFormatting sqref="C3:C10">
+    <cfRule type="top10" dxfId="22" priority="56" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13:C22">
-    <cfRule type="top10" dxfId="21" priority="89" rank="1"/>
+  <conditionalFormatting sqref="C14:C24">
+    <cfRule type="top10" dxfId="21" priority="101" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D9">
-    <cfRule type="top10" dxfId="20" priority="40" bottom="1" rank="1"/>
+  <conditionalFormatting sqref="D3:D10">
+    <cfRule type="top10" dxfId="20" priority="12" bottom="1" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D13:D22">
-    <cfRule type="top10" dxfId="19" priority="91" bottom="1" rank="1"/>
+  <conditionalFormatting sqref="D14:D24">
+    <cfRule type="top10" dxfId="19" priority="6" bottom="1" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E9">
-    <cfRule type="top10" dxfId="18" priority="31" rank="1"/>
+  <conditionalFormatting sqref="E3:E10">
+    <cfRule type="top10" dxfId="18" priority="9" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E22">
-    <cfRule type="top10" dxfId="17" priority="97" rank="1"/>
+  <conditionalFormatting sqref="E14:E24">
+    <cfRule type="top10" dxfId="17" priority="3" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F9">
-    <cfRule type="top10" dxfId="16" priority="33" bottom="1" rank="1"/>
+  <conditionalFormatting sqref="F3:F10">
+    <cfRule type="top10" dxfId="16" priority="11" bottom="1" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F22">
-    <cfRule type="top10" dxfId="15" priority="93" bottom="1" rank="1"/>
+  <conditionalFormatting sqref="F14:F24">
+    <cfRule type="top10" dxfId="15" priority="5" bottom="1" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G9">
-    <cfRule type="top10" dxfId="14" priority="30" rank="1"/>
+  <conditionalFormatting sqref="G3:G10">
+    <cfRule type="top10" dxfId="14" priority="8" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13:G22">
-    <cfRule type="top10" dxfId="13" priority="99" rank="1"/>
+  <conditionalFormatting sqref="G14:G24">
+    <cfRule type="top10" dxfId="13" priority="2" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H9">
-    <cfRule type="top10" dxfId="12" priority="32" bottom="1" rank="1"/>
+  <conditionalFormatting sqref="H3:H10">
+    <cfRule type="top10" dxfId="12" priority="10" bottom="1" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13:H22">
-    <cfRule type="top10" dxfId="11" priority="95" bottom="1" rank="1"/>
+  <conditionalFormatting sqref="H14:H24">
+    <cfRule type="top10" dxfId="11" priority="4" bottom="1" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I9">
-    <cfRule type="top10" dxfId="10" priority="29" rank="1"/>
+  <conditionalFormatting sqref="I3:I10">
+    <cfRule type="top10" dxfId="10" priority="7" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I13:I22">
-    <cfRule type="top10" dxfId="9" priority="101" rank="1"/>
+  <conditionalFormatting sqref="I14:I24">
+    <cfRule type="top10" dxfId="9" priority="1" rank="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1667,32 +1749,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80150BC0-64DC-411B-A1B1-FAD28F14CD71}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.20703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11" t="s">
+      <c r="G1" s="13"/>
+      <c r="H1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="11"/>
+      <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1"/>
@@ -1726,28 +1809,28 @@
         <v>16</v>
       </c>
       <c r="B3" s="1">
-        <v>0.23350000000000001</v>
+        <v>0.2349</v>
       </c>
       <c r="C3" s="1">
-        <v>0.14399999999999999</v>
+        <v>0.13819999999999999</v>
       </c>
       <c r="D3" s="1">
-        <v>0.23130000000000001</v>
+        <v>0.23119999999999999</v>
       </c>
       <c r="E3" s="1">
-        <v>0.1646</v>
+        <v>0.16539999999999999</v>
       </c>
       <c r="F3" s="1">
+        <v>0.2152</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="H3" s="1">
         <v>0.21540000000000001</v>
       </c>
-      <c r="G3" s="1">
-        <v>0.25409999999999999</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0.22020000000000001</v>
-      </c>
       <c r="I3" s="1">
-        <v>0.21460000000000001</v>
+        <v>0.2346</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1755,28 +1838,28 @@
         <v>17</v>
       </c>
       <c r="B4" s="1">
-        <v>0.2366</v>
+        <v>0.2364</v>
       </c>
       <c r="C4" s="1">
-        <v>0.1298</v>
+        <v>0.12909999999999999</v>
       </c>
       <c r="D4" s="1">
-        <v>0.23230000000000001</v>
+        <v>0.2319</v>
       </c>
       <c r="E4" s="1">
-        <v>0.16270000000000001</v>
+        <v>0.16619999999999999</v>
       </c>
       <c r="F4" s="1">
         <v>0.21249999999999999</v>
       </c>
       <c r="G4" s="1">
-        <v>0.27660000000000001</v>
+        <v>0.27650000000000002</v>
       </c>
       <c r="H4" s="1">
-        <v>0.2152</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="I4" s="1">
-        <v>0.2369</v>
+        <v>0.26069999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1784,28 +1867,28 @@
         <v>18</v>
       </c>
       <c r="B5" s="1">
-        <v>0.23769999999999999</v>
+        <v>0.23749999999999999</v>
       </c>
       <c r="C5" s="1">
-        <v>9.8299999999999998E-2</v>
+        <v>9.7600000000000006E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>0.2366</v>
+        <v>0.2364</v>
       </c>
       <c r="E5" s="1">
-        <v>0.1447</v>
+        <v>0.14749999999999999</v>
       </c>
       <c r="F5" s="1">
-        <v>0.21179999999999999</v>
+        <v>0.2117</v>
       </c>
       <c r="G5" s="1">
-        <v>0.2646</v>
+        <v>0.26329999999999998</v>
       </c>
       <c r="H5" s="1">
-        <v>0.21609999999999999</v>
+        <v>0.2107</v>
       </c>
       <c r="I5" s="1">
-        <v>0.22140000000000001</v>
+        <v>0.26879999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1813,28 +1896,28 @@
         <v>19</v>
       </c>
       <c r="B6" s="1">
-        <v>0.2387</v>
+        <v>0.23980000000000001</v>
       </c>
       <c r="C6" s="1">
-        <v>8.1500000000000003E-2</v>
+        <v>7.8600000000000003E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>0.2306</v>
+        <v>0.2301</v>
       </c>
       <c r="E6" s="1">
-        <v>0.15759999999999999</v>
+        <v>0.18809999999999999</v>
       </c>
       <c r="F6" s="1">
-        <v>0.20699999999999999</v>
+        <v>0.2069</v>
       </c>
       <c r="G6" s="1">
-        <v>0.2873</v>
+        <v>0.27739999999999998</v>
       </c>
       <c r="H6" s="1">
-        <v>0.2094</v>
+        <v>0.2074</v>
       </c>
       <c r="I6" s="1">
-        <v>0.248</v>
+        <v>0.25650000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1842,28 +1925,28 @@
         <v>20</v>
       </c>
       <c r="B7" s="1">
-        <v>0.24129999999999999</v>
+        <v>0.24179999999999999</v>
       </c>
       <c r="C7" s="1">
-        <v>4.9000000000000002E-2</v>
+        <v>5.0799999999999998E-2</v>
       </c>
       <c r="D7" s="1">
         <v>0.23019999999999999</v>
       </c>
       <c r="E7" s="1">
-        <v>0.16839999999999999</v>
+        <v>0.16880000000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>0.20810000000000001</v>
+        <v>0.2069</v>
       </c>
       <c r="G7" s="1">
-        <v>0.28860000000000002</v>
+        <v>0.29609999999999997</v>
       </c>
       <c r="H7" s="1">
-        <v>0.21</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="I7" s="1">
-        <v>0.24060000000000001</v>
+        <v>0.28029999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1871,28 +1954,28 @@
         <v>24</v>
       </c>
       <c r="B8" s="1">
-        <v>0.2261</v>
+        <v>0.22589999999999999</v>
       </c>
       <c r="C8" s="1">
-        <v>0.16950000000000001</v>
+        <v>0.17180000000000001</v>
       </c>
       <c r="D8" s="1">
-        <v>0.22570000000000001</v>
+        <v>0.22550000000000001</v>
       </c>
       <c r="E8" s="1">
-        <v>0.1696</v>
+        <v>0.17180000000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>0.2024</v>
+        <v>0.2026</v>
       </c>
       <c r="G8" s="1">
-        <v>0.2843</v>
+        <v>0.28439999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>0.20710000000000001</v>
+        <v>0.20530000000000001</v>
       </c>
       <c r="I8" s="1">
-        <v>0.2369</v>
+        <v>0.25819999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1900,28 +1983,28 @@
         <v>21</v>
       </c>
       <c r="B9" s="1">
-        <v>0.23080000000000001</v>
+        <v>0.2306</v>
       </c>
       <c r="C9" s="1">
-        <v>0.17</v>
+        <v>0.17130000000000001</v>
       </c>
       <c r="D9" s="1">
-        <v>0.2306</v>
+        <v>0.23050000000000001</v>
       </c>
       <c r="E9" s="1">
-        <v>0.17030000000000001</v>
+        <v>0.1714</v>
       </c>
       <c r="F9" s="1">
-        <v>0.2097</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="G9" s="1">
-        <v>0.28599999999999998</v>
+        <v>0.29120000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>0.21240000000000001</v>
+        <v>0.20880000000000001</v>
       </c>
       <c r="I9" s="1">
-        <v>0.2414</v>
+        <v>0.27500000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1929,28 +2012,28 @@
         <v>22</v>
       </c>
       <c r="B10" s="1">
-        <v>0.2303</v>
+        <v>0.23</v>
       </c>
       <c r="C10" s="1">
-        <v>0.17030000000000001</v>
+        <v>0.17280000000000001</v>
       </c>
       <c r="D10" s="1">
         <v>0.2301</v>
       </c>
       <c r="E10" s="1">
-        <v>0.1711</v>
+        <v>0.17280000000000001</v>
       </c>
       <c r="F10" s="1">
-        <v>0.2084</v>
+        <v>0.2082</v>
       </c>
       <c r="G10" s="1">
-        <v>0.28920000000000001</v>
+        <v>0.2893</v>
       </c>
       <c r="H10" s="1">
-        <v>0.2109</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="I10" s="1">
-        <v>0.24640000000000001</v>
+        <v>0.27229999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1958,28 +2041,28 @@
         <v>52</v>
       </c>
       <c r="B11" s="1">
-        <v>0.2293</v>
+        <v>0.2296</v>
       </c>
       <c r="C11" s="1">
-        <v>0.17430000000000001</v>
+        <v>0.1749</v>
       </c>
       <c r="D11" s="1">
-        <v>0.2288</v>
+        <v>0.2291</v>
       </c>
       <c r="E11" s="1">
-        <v>0.17760000000000001</v>
+        <v>0.1779</v>
       </c>
       <c r="F11" s="1">
-        <v>0.20799999999999999</v>
+        <v>0.2074</v>
       </c>
       <c r="G11" s="1">
-        <v>0.29189999999999999</v>
+        <v>0.29459999999999997</v>
       </c>
       <c r="H11" s="1">
-        <v>0.21060000000000001</v>
+        <v>0.2077</v>
       </c>
       <c r="I11" s="1">
-        <v>0.25180000000000002</v>
+        <v>0.2787</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1990,25 +2073,25 @@
         <v>0.2276</v>
       </c>
       <c r="C12" s="1">
-        <v>0.17660000000000001</v>
+        <v>0.17829999999999999</v>
       </c>
       <c r="D12" s="1">
-        <v>0.22689999999999999</v>
+        <v>0.22670000000000001</v>
       </c>
       <c r="E12" s="1">
-        <v>0.1789</v>
+        <v>0.17929999999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>0.20499999999999999</v>
+        <v>0.20369999999999999</v>
       </c>
       <c r="G12" s="1">
-        <v>0.29420000000000002</v>
+        <v>0.29289999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>0.20810000000000001</v>
+        <v>0.2056</v>
       </c>
       <c r="I12" s="1">
-        <v>0.24890000000000001</v>
+        <v>0.2727</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2016,28 +2099,28 @@
         <v>23</v>
       </c>
       <c r="B13" s="1">
-        <v>0.22869999999999999</v>
+        <v>0.22919999999999999</v>
       </c>
       <c r="C13" s="1">
-        <v>0.1789</v>
+        <v>0.17849999999999999</v>
       </c>
       <c r="D13" s="1">
-        <v>0.2273</v>
+        <v>0.2278</v>
       </c>
       <c r="E13" s="1">
-        <v>0.18160000000000001</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="F13" s="1">
-        <v>0.20669999999999999</v>
+        <v>0.20619999999999999</v>
       </c>
       <c r="G13" s="1">
-        <v>0.2903</v>
+        <v>0.29459999999999997</v>
       </c>
       <c r="H13" s="1">
-        <v>0.21029999999999999</v>
+        <v>0.20730000000000001</v>
       </c>
       <c r="I13" s="1">
-        <v>0.25169999999999998</v>
+        <v>0.27200000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2045,28 +2128,28 @@
         <v>56</v>
       </c>
       <c r="B14" s="1">
-        <v>0.23130000000000001</v>
+        <v>0.23139999999999999</v>
       </c>
       <c r="C14" s="1">
-        <v>0.16300000000000001</v>
+        <v>0.1638</v>
       </c>
       <c r="D14" s="1">
         <v>0.23089999999999999</v>
       </c>
       <c r="E14" s="1">
-        <v>0.1678</v>
+        <v>0.16880000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>0.2099</v>
+        <v>0.20930000000000001</v>
       </c>
       <c r="G14" s="1">
-        <v>0.2868</v>
+        <v>0.29020000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>0.21260000000000001</v>
+        <v>0.20910000000000001</v>
       </c>
       <c r="I14" s="1">
-        <v>0.24390000000000001</v>
+        <v>0.28120000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2074,28 +2157,28 @@
         <v>60</v>
       </c>
       <c r="B15" s="1">
-        <v>0.23080000000000001</v>
+        <v>0.23069999999999999</v>
       </c>
       <c r="C15" s="1">
-        <v>0.16520000000000001</v>
+        <v>0.16719999999999999</v>
       </c>
       <c r="D15" s="1">
-        <v>0.2301</v>
+        <v>0.23</v>
       </c>
       <c r="E15" s="1">
-        <v>0.17019999999999999</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="F15" s="1">
-        <v>0.2084</v>
+        <v>0.2077</v>
       </c>
       <c r="G15" s="1">
-        <v>0.29010000000000002</v>
+        <v>0.29189999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>0.2117</v>
+        <v>0.20730000000000001</v>
       </c>
       <c r="I15" s="1">
-        <v>0.24759999999999999</v>
+        <v>0.27800000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2103,28 +2186,28 @@
         <v>54</v>
       </c>
       <c r="B16" s="1">
-        <v>0.23080000000000001</v>
+        <v>0.2303</v>
       </c>
       <c r="C16" s="1">
-        <v>0.16619999999999999</v>
+        <v>0.1704</v>
       </c>
       <c r="D16" s="1">
-        <v>0.23100000000000001</v>
+        <v>0.23050000000000001</v>
       </c>
       <c r="E16" s="1">
-        <v>0.16639999999999999</v>
+        <v>0.17050000000000001</v>
       </c>
       <c r="F16" s="1">
-        <v>0.2094</v>
+        <v>0.2092</v>
       </c>
       <c r="G16" s="1">
-        <v>0.28649999999999998</v>
+        <v>0.2828</v>
       </c>
       <c r="H16" s="1">
-        <v>0.21160000000000001</v>
+        <v>0.2092</v>
       </c>
       <c r="I16" s="1">
-        <v>0.2472</v>
+        <v>0.2651</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2132,28 +2215,28 @@
         <v>57</v>
       </c>
       <c r="B17" s="1">
-        <v>0.2298</v>
+        <v>0.2296</v>
       </c>
       <c r="C17" s="1">
-        <v>0.1691</v>
+        <v>0.1714</v>
       </c>
       <c r="D17" s="1">
-        <v>0.22989999999999999</v>
+        <v>0.2296</v>
       </c>
       <c r="E17" s="1">
-        <v>0.17030000000000001</v>
+        <v>0.1719</v>
       </c>
       <c r="F17" s="1">
-        <v>0.20730000000000001</v>
+        <v>0.20649999999999999</v>
       </c>
       <c r="G17" s="1">
-        <v>0.29060000000000002</v>
+        <v>0.29339999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>0.2092</v>
+        <v>0.20610000000000001</v>
       </c>
       <c r="I17" s="1">
-        <v>0.24729999999999999</v>
+        <v>0.27639999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2164,25 +2247,25 @@
         <v>0.2291</v>
       </c>
       <c r="C18" s="1">
-        <v>0.1726</v>
+        <v>0.17430000000000001</v>
       </c>
       <c r="D18" s="1">
-        <v>0.22770000000000001</v>
+        <v>0.2276</v>
       </c>
       <c r="E18" s="1">
-        <v>0.17649999999999999</v>
+        <v>0.17860000000000001</v>
       </c>
       <c r="F18" s="1">
-        <v>0.20519999999999999</v>
+        <v>0.2049</v>
       </c>
       <c r="G18" s="1">
-        <v>0.29459999999999997</v>
+        <v>0.29260000000000003</v>
       </c>
       <c r="H18" s="1">
-        <v>0.20860000000000001</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="I18" s="1">
-        <v>0.2505</v>
+        <v>0.2737</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2190,28 +2273,28 @@
         <v>59</v>
       </c>
       <c r="B19" s="1">
-        <v>0.23150000000000001</v>
+        <v>0.23169999999999999</v>
       </c>
       <c r="C19" s="1">
-        <v>0.15629999999999999</v>
+        <v>0.15609999999999999</v>
       </c>
       <c r="D19" s="1">
-        <v>0.23019999999999999</v>
+        <v>0.23039999999999999</v>
       </c>
       <c r="E19" s="1">
-        <v>0.16869999999999999</v>
+        <v>0.16880000000000001</v>
       </c>
       <c r="F19" s="1">
-        <v>0.2084</v>
+        <v>0.2074</v>
       </c>
       <c r="G19" s="1">
-        <v>0.28939999999999999</v>
+        <v>0.29480000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>0.2109</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="I19" s="1">
-        <v>0.24390000000000001</v>
+        <v>0.28510000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2219,28 +2302,28 @@
         <v>61</v>
       </c>
       <c r="B20" s="1">
-        <v>0.23250000000000001</v>
+        <v>0.23230000000000001</v>
       </c>
       <c r="C20" s="1">
-        <v>0.14510000000000001</v>
+        <v>0.14779999999999999</v>
       </c>
       <c r="D20" s="1">
-        <v>0.2306</v>
+        <v>0.2301</v>
       </c>
       <c r="E20" s="1">
-        <v>0.15770000000000001</v>
+        <v>0.16239999999999999</v>
       </c>
       <c r="F20" s="1">
-        <v>0.20710000000000001</v>
+        <v>0.2069</v>
       </c>
       <c r="G20" s="1">
-        <v>0.28739999999999999</v>
+        <v>0.2777</v>
       </c>
       <c r="H20" s="1">
-        <v>0.2094</v>
+        <v>0.20810000000000001</v>
       </c>
       <c r="I20" s="1">
-        <v>0.2482</v>
+        <v>0.27689999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2291,6 +2374,20 @@
       </c>
       <c r="D24">
         <v>0.24890000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="4">
+        <v>46112</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25">
+        <v>0.2056</v>
+      </c>
+      <c r="D25">
+        <v>0.2727</v>
       </c>
     </row>
   </sheetData>
@@ -2306,7 +2403,7 @@
   <conditionalFormatting sqref="C3:C20">
     <cfRule type="top10" dxfId="7" priority="117" rank="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D20 D23:D24">
+  <conditionalFormatting sqref="D3:D20 D23:D25">
     <cfRule type="top10" dxfId="6" priority="6" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E20">
@@ -6290,7 +6387,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>30</v>
       </c>
@@ -6330,7 +6427,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>46</v>
       </c>
@@ -6370,7 +6467,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>32</v>
       </c>
@@ -6410,7 +6507,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>26</v>
       </c>
@@ -6450,7 +6547,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>43</v>
       </c>
@@ -6490,85 +6587,1010 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B102" s="6">
+        <v>7.76</v>
+      </c>
+      <c r="C102" s="5">
+        <f>B102-L102</f>
+        <v>2.2699999999999996</v>
+      </c>
+      <c r="D102" s="5">
+        <f>B102+L102</f>
+        <v>13.25</v>
+      </c>
+      <c r="E102" s="5">
+        <v>2.27</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" s="8">
+        <v>1</v>
+      </c>
       <c r="H102" s="8"/>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I102" t="s">
+        <v>88</v>
+      </c>
+      <c r="J102" t="s">
+        <v>82</v>
+      </c>
+      <c r="K102" t="s">
+        <v>77</v>
+      </c>
+      <c r="L102">
+        <v>5.49</v>
+      </c>
+      <c r="N102" s="6"/>
+      <c r="O102" s="5"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" s="6">
+        <v>7.95</v>
+      </c>
+      <c r="C103" s="5">
+        <f t="shared" ref="C103:C126" si="8">B103-L103</f>
+        <v>2.46</v>
+      </c>
+      <c r="D103" s="5">
+        <f t="shared" ref="D103:D126" si="9">B103+L103</f>
+        <v>13.440000000000001</v>
+      </c>
+      <c r="E103" s="5">
+        <v>7.95</v>
+      </c>
+      <c r="F103">
+        <v>2</v>
+      </c>
+      <c r="G103" s="8">
+        <v>7</v>
+      </c>
       <c r="H103" s="8"/>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I103" t="s">
+        <v>88</v>
+      </c>
+      <c r="J103" t="s">
+        <v>82</v>
+      </c>
+      <c r="K103" t="s">
+        <v>77</v>
+      </c>
+      <c r="L103">
+        <v>5.49</v>
+      </c>
+      <c r="N103" s="6"/>
+      <c r="O103" s="5"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" s="6">
+        <v>8.18</v>
+      </c>
+      <c r="C104" s="5">
+        <f t="shared" si="8"/>
+        <v>2.6899999999999995</v>
+      </c>
+      <c r="D104" s="5">
+        <f t="shared" si="9"/>
+        <v>13.67</v>
+      </c>
+      <c r="E104" s="5">
+        <v>2.69</v>
+      </c>
+      <c r="F104">
+        <v>3</v>
+      </c>
+      <c r="G104" s="8">
+        <v>2</v>
+      </c>
       <c r="H104" s="8"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I104" t="s">
+        <v>88</v>
+      </c>
+      <c r="J104" t="s">
+        <v>82</v>
+      </c>
+      <c r="K104" t="s">
+        <v>77</v>
+      </c>
+      <c r="L104">
+        <v>5.49</v>
+      </c>
+      <c r="N104" s="6"/>
+      <c r="O104" s="5"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B105" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="C105" s="5">
+        <f t="shared" si="8"/>
+        <v>3.01</v>
+      </c>
+      <c r="D105" s="5">
+        <f t="shared" si="9"/>
+        <v>13.99</v>
+      </c>
+      <c r="E105" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="F105">
+        <v>4</v>
+      </c>
+      <c r="G105" s="8">
+        <v>8</v>
+      </c>
       <c r="H105" s="8"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I105" t="s">
+        <v>88</v>
+      </c>
+      <c r="J105" t="s">
+        <v>82</v>
+      </c>
+      <c r="K105" t="s">
+        <v>77</v>
+      </c>
+      <c r="L105">
+        <v>5.49</v>
+      </c>
+      <c r="N105" s="6"/>
+      <c r="O105" s="5"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B106" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="C106" s="5">
+        <f t="shared" si="8"/>
+        <v>3.6099999999999994</v>
+      </c>
+      <c r="D106" s="5">
+        <f t="shared" si="9"/>
+        <v>14.59</v>
+      </c>
+      <c r="E106" s="5">
+        <v>9.1</v>
+      </c>
+      <c r="F106">
+        <v>5</v>
+      </c>
+      <c r="G106" s="8">
+        <v>9</v>
+      </c>
       <c r="H106" s="8"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I106" t="s">
+        <v>88</v>
+      </c>
+      <c r="J106" t="s">
+        <v>82</v>
+      </c>
+      <c r="K106" t="s">
+        <v>77</v>
+      </c>
+      <c r="L106">
+        <v>5.49</v>
+      </c>
+      <c r="N106" s="6"/>
+      <c r="O106" s="5"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B107" s="6">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="C107" s="5">
+        <f t="shared" si="8"/>
+        <v>3.7899999999999991</v>
+      </c>
+      <c r="D107" s="5">
+        <f t="shared" si="9"/>
+        <v>14.77</v>
+      </c>
+      <c r="E107" s="5">
+        <v>3.79</v>
+      </c>
+      <c r="F107">
+        <v>6</v>
+      </c>
+      <c r="G107" s="8">
+        <v>3</v>
+      </c>
       <c r="H107" s="8"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I107" t="s">
+        <v>88</v>
+      </c>
+      <c r="J107" t="s">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s">
+        <v>77</v>
+      </c>
+      <c r="L107">
+        <v>5.49</v>
+      </c>
+      <c r="N107" s="6"/>
+      <c r="O107" s="5"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B108" s="6">
+        <v>9.81</v>
+      </c>
+      <c r="C108" s="5">
+        <f t="shared" si="8"/>
+        <v>4.32</v>
+      </c>
+      <c r="D108" s="5">
+        <f t="shared" si="9"/>
+        <v>15.3</v>
+      </c>
+      <c r="E108" s="5">
+        <v>4.32</v>
+      </c>
+      <c r="F108">
+        <v>7</v>
+      </c>
+      <c r="G108" s="8">
+        <v>4</v>
+      </c>
       <c r="H108" s="8"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I108" t="s">
+        <v>88</v>
+      </c>
+      <c r="J108" t="s">
+        <v>82</v>
+      </c>
+      <c r="K108" t="s">
+        <v>77</v>
+      </c>
+      <c r="L108">
+        <v>5.49</v>
+      </c>
+      <c r="N108" s="6"/>
+      <c r="O108" s="5"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" s="6">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="C109" s="5">
+        <f t="shared" si="8"/>
+        <v>4.4700000000000006</v>
+      </c>
+      <c r="D109" s="5">
+        <f t="shared" si="9"/>
+        <v>15.450000000000001</v>
+      </c>
+      <c r="E109" s="5">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="F109">
+        <v>8</v>
+      </c>
+      <c r="G109" s="8">
+        <v>11</v>
+      </c>
       <c r="H109" s="8"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I109" t="s">
+        <v>88</v>
+      </c>
+      <c r="J109" t="s">
+        <v>82</v>
+      </c>
+      <c r="K109" t="s">
+        <v>77</v>
+      </c>
+      <c r="L109">
+        <v>5.49</v>
+      </c>
+      <c r="N109" s="6"/>
+      <c r="O109" s="5"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" s="6">
+        <v>10.36</v>
+      </c>
+      <c r="C110" s="5">
+        <f t="shared" si="8"/>
+        <v>4.8699999999999992</v>
+      </c>
+      <c r="D110" s="5">
+        <f t="shared" si="9"/>
+        <v>15.85</v>
+      </c>
+      <c r="E110" s="5">
+        <v>4.87</v>
+      </c>
+      <c r="F110">
+        <v>9</v>
+      </c>
+      <c r="G110" s="8">
+        <v>5</v>
+      </c>
       <c r="H110" s="8"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I110" t="s">
+        <v>88</v>
+      </c>
+      <c r="J110" t="s">
+        <v>82</v>
+      </c>
+      <c r="K110" t="s">
+        <v>77</v>
+      </c>
+      <c r="L110">
+        <v>5.49</v>
+      </c>
+      <c r="N110" s="6"/>
+      <c r="O110" s="5"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B111" s="6">
+        <v>10.65</v>
+      </c>
+      <c r="C111" s="5">
+        <f t="shared" si="8"/>
+        <v>5.16</v>
+      </c>
+      <c r="D111" s="5">
+        <f t="shared" si="9"/>
+        <v>16.14</v>
+      </c>
+      <c r="E111" s="5">
+        <v>5.16</v>
+      </c>
+      <c r="F111">
+        <v>10</v>
+      </c>
+      <c r="G111" s="8">
+        <v>6</v>
+      </c>
       <c r="H111" s="8"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="I111" t="s">
+        <v>88</v>
+      </c>
+      <c r="J111" t="s">
+        <v>82</v>
+      </c>
+      <c r="K111" t="s">
+        <v>77</v>
+      </c>
+      <c r="L111">
+        <v>5.49</v>
+      </c>
+      <c r="N111" s="6"/>
+      <c r="O111" s="5"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" s="6">
+        <v>10.85</v>
+      </c>
+      <c r="C112" s="5">
+        <f t="shared" si="8"/>
+        <v>5.3599999999999994</v>
+      </c>
+      <c r="D112" s="5">
+        <f t="shared" si="9"/>
+        <v>16.34</v>
+      </c>
+      <c r="E112" s="5">
+        <v>10.85</v>
+      </c>
+      <c r="F112">
+        <v>11</v>
+      </c>
+      <c r="G112" s="8">
+        <v>12</v>
+      </c>
       <c r="H112" s="8"/>
-    </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I112" t="s">
+        <v>88</v>
+      </c>
+      <c r="J112" t="s">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s">
+        <v>77</v>
+      </c>
+      <c r="L112">
+        <v>5.49</v>
+      </c>
+      <c r="N112" s="6"/>
+      <c r="O112" s="5"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B113" s="6">
+        <v>11.79</v>
+      </c>
+      <c r="C113" s="5">
+        <f t="shared" si="8"/>
+        <v>6.2999999999999989</v>
+      </c>
+      <c r="D113" s="5">
+        <f t="shared" si="9"/>
+        <v>17.28</v>
+      </c>
+      <c r="E113" s="5">
+        <v>11.79</v>
+      </c>
+      <c r="F113">
+        <v>12</v>
+      </c>
+      <c r="G113" s="8">
+        <v>13</v>
+      </c>
       <c r="H113" s="8"/>
-    </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I113" t="s">
+        <v>88</v>
+      </c>
+      <c r="J113" t="s">
+        <v>82</v>
+      </c>
+      <c r="K113" t="s">
+        <v>77</v>
+      </c>
+      <c r="L113">
+        <v>5.49</v>
+      </c>
+      <c r="N113" s="6"/>
+      <c r="O113" s="5"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B114" s="6">
+        <v>11.81</v>
+      </c>
+      <c r="C114" s="5">
+        <f t="shared" si="8"/>
+        <v>6.32</v>
+      </c>
+      <c r="D114" s="5">
+        <f t="shared" si="9"/>
+        <v>17.3</v>
+      </c>
+      <c r="E114" s="5">
+        <v>11.81</v>
+      </c>
+      <c r="F114">
+        <v>13</v>
+      </c>
+      <c r="G114" s="8">
+        <v>14</v>
+      </c>
       <c r="H114" s="8"/>
-    </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I114" t="s">
+        <v>88</v>
+      </c>
+      <c r="J114" t="s">
+        <v>82</v>
+      </c>
+      <c r="K114" t="s">
+        <v>77</v>
+      </c>
+      <c r="L114">
+        <v>5.49</v>
+      </c>
+      <c r="N114" s="6"/>
+      <c r="O114" s="5"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B115" s="6">
+        <v>12.17</v>
+      </c>
+      <c r="C115" s="5">
+        <f t="shared" si="8"/>
+        <v>6.68</v>
+      </c>
+      <c r="D115" s="5">
+        <f t="shared" si="9"/>
+        <v>17.66</v>
+      </c>
+      <c r="E115" s="5">
+        <v>12.17</v>
+      </c>
+      <c r="F115">
+        <v>14</v>
+      </c>
+      <c r="G115" s="8">
+        <v>15</v>
+      </c>
       <c r="H115" s="8"/>
-    </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I115" t="s">
+        <v>88</v>
+      </c>
+      <c r="J115" t="s">
+        <v>82</v>
+      </c>
+      <c r="K115" t="s">
+        <v>77</v>
+      </c>
+      <c r="L115">
+        <v>5.49</v>
+      </c>
+      <c r="N115" s="6"/>
+      <c r="O115" s="5"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B116" s="6">
+        <v>12.49</v>
+      </c>
+      <c r="C116" s="5">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="D116" s="5">
+        <f t="shared" si="9"/>
+        <v>17.98</v>
+      </c>
+      <c r="E116" s="5">
+        <v>12.49</v>
+      </c>
+      <c r="F116">
+        <v>15</v>
+      </c>
+      <c r="G116" s="8">
+        <v>16</v>
+      </c>
       <c r="H116" s="8"/>
-    </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I116" t="s">
+        <v>88</v>
+      </c>
+      <c r="J116" t="s">
+        <v>82</v>
+      </c>
+      <c r="K116" t="s">
+        <v>77</v>
+      </c>
+      <c r="L116">
+        <v>5.49</v>
+      </c>
+      <c r="N116" s="6"/>
+      <c r="O116" s="5"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B117" s="6">
+        <v>14.34</v>
+      </c>
+      <c r="C117" s="5">
+        <f t="shared" si="8"/>
+        <v>8.85</v>
+      </c>
+      <c r="D117" s="5">
+        <f t="shared" si="9"/>
+        <v>19.829999999999998</v>
+      </c>
+      <c r="E117" s="5">
+        <v>14.34</v>
+      </c>
+      <c r="F117">
+        <v>16</v>
+      </c>
+      <c r="G117" s="8">
+        <v>17</v>
+      </c>
       <c r="H117" s="8"/>
-    </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I117" t="s">
+        <v>88</v>
+      </c>
+      <c r="J117" t="s">
+        <v>82</v>
+      </c>
+      <c r="K117" t="s">
+        <v>77</v>
+      </c>
+      <c r="L117">
+        <v>5.49</v>
+      </c>
+      <c r="N117" s="6"/>
+      <c r="O117" s="5"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B118" s="6">
+        <v>14.41</v>
+      </c>
+      <c r="C118" s="5">
+        <f t="shared" si="8"/>
+        <v>8.92</v>
+      </c>
+      <c r="D118" s="5">
+        <f t="shared" si="9"/>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E118" s="5">
+        <v>14.41</v>
+      </c>
+      <c r="F118">
+        <v>17</v>
+      </c>
+      <c r="G118" s="8">
+        <v>18</v>
+      </c>
       <c r="H118" s="8"/>
-    </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I118" t="s">
+        <v>88</v>
+      </c>
+      <c r="J118" t="s">
+        <v>82</v>
+      </c>
+      <c r="K118" t="s">
+        <v>77</v>
+      </c>
+      <c r="L118">
+        <v>5.49</v>
+      </c>
+      <c r="N118" s="6"/>
+      <c r="O118" s="5"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B119" s="6">
+        <v>14.42</v>
+      </c>
+      <c r="C119" s="5">
+        <f t="shared" si="8"/>
+        <v>8.93</v>
+      </c>
+      <c r="D119" s="5">
+        <f t="shared" si="9"/>
+        <v>19.91</v>
+      </c>
+      <c r="E119" s="5">
+        <v>19.91</v>
+      </c>
+      <c r="F119">
+        <v>18</v>
+      </c>
+      <c r="G119" s="8">
+        <v>23</v>
+      </c>
       <c r="H119" s="8"/>
-    </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I119" t="s">
+        <v>88</v>
+      </c>
+      <c r="J119" t="s">
+        <v>82</v>
+      </c>
+      <c r="K119" t="s">
+        <v>77</v>
+      </c>
+      <c r="L119">
+        <v>5.49</v>
+      </c>
+      <c r="N119" s="6"/>
+      <c r="O119" s="5"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B120" s="6">
+        <v>14.55</v>
+      </c>
+      <c r="C120" s="5">
+        <f t="shared" si="8"/>
+        <v>9.06</v>
+      </c>
+      <c r="D120" s="5">
+        <f t="shared" si="9"/>
+        <v>20.04</v>
+      </c>
+      <c r="E120" s="5">
+        <v>14.55</v>
+      </c>
+      <c r="F120">
+        <v>19</v>
+      </c>
+      <c r="G120" s="8">
+        <v>19</v>
+      </c>
       <c r="H120" s="8"/>
-    </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I120" t="s">
+        <v>88</v>
+      </c>
+      <c r="J120" t="s">
+        <v>82</v>
+      </c>
+      <c r="K120" t="s">
+        <v>77</v>
+      </c>
+      <c r="L120">
+        <v>5.49</v>
+      </c>
+      <c r="N120" s="6"/>
+      <c r="O120" s="5"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B121" s="6">
+        <v>14.66</v>
+      </c>
+      <c r="C121" s="5">
+        <f t="shared" si="8"/>
+        <v>9.17</v>
+      </c>
+      <c r="D121" s="5">
+        <f t="shared" si="9"/>
+        <v>20.149999999999999</v>
+      </c>
+      <c r="E121" s="5">
+        <v>9.17</v>
+      </c>
+      <c r="F121">
+        <v>20</v>
+      </c>
+      <c r="G121" s="8">
+        <v>10</v>
+      </c>
       <c r="H121" s="8"/>
-    </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I121" t="s">
+        <v>88</v>
+      </c>
+      <c r="J121" t="s">
+        <v>82</v>
+      </c>
+      <c r="K121" t="s">
+        <v>77</v>
+      </c>
+      <c r="L121">
+        <v>5.49</v>
+      </c>
+      <c r="N121" s="6"/>
+      <c r="O121" s="5"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B122" s="6">
+        <v>14.86</v>
+      </c>
+      <c r="C122" s="5">
+        <f t="shared" si="8"/>
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="D122" s="5">
+        <f t="shared" si="9"/>
+        <v>20.350000000000001</v>
+      </c>
+      <c r="E122" s="5">
+        <v>14.86</v>
+      </c>
+      <c r="F122">
+        <v>21</v>
+      </c>
+      <c r="G122" s="8">
+        <v>20</v>
+      </c>
       <c r="H122" s="8"/>
-    </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I122" t="s">
+        <v>88</v>
+      </c>
+      <c r="J122" t="s">
+        <v>82</v>
+      </c>
+      <c r="K122" t="s">
+        <v>77</v>
+      </c>
+      <c r="L122">
+        <v>5.49</v>
+      </c>
+      <c r="N122" s="6"/>
+      <c r="O122" s="5"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B123" s="6">
+        <v>15.43</v>
+      </c>
+      <c r="C123" s="5">
+        <f t="shared" si="8"/>
+        <v>9.94</v>
+      </c>
+      <c r="D123" s="5">
+        <f t="shared" si="9"/>
+        <v>20.92</v>
+      </c>
+      <c r="E123" s="5">
+        <v>15.43</v>
+      </c>
+      <c r="F123">
+        <v>22</v>
+      </c>
+      <c r="G123" s="8">
+        <v>21</v>
+      </c>
       <c r="H123" s="8"/>
-    </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I123" t="s">
+        <v>88</v>
+      </c>
+      <c r="J123" t="s">
+        <v>82</v>
+      </c>
+      <c r="K123" t="s">
+        <v>77</v>
+      </c>
+      <c r="L123">
+        <v>5.49</v>
+      </c>
+      <c r="N123" s="6"/>
+      <c r="O123" s="5"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B124" s="6">
+        <v>15.97</v>
+      </c>
+      <c r="C124" s="5">
+        <f t="shared" si="8"/>
+        <v>10.48</v>
+      </c>
+      <c r="D124" s="5">
+        <f t="shared" si="9"/>
+        <v>21.46</v>
+      </c>
+      <c r="E124" s="5">
+        <v>21.46</v>
+      </c>
+      <c r="F124">
+        <v>23</v>
+      </c>
+      <c r="G124" s="8">
+        <v>24</v>
+      </c>
       <c r="H124" s="8"/>
-    </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I124" t="s">
+        <v>88</v>
+      </c>
+      <c r="J124" t="s">
+        <v>82</v>
+      </c>
+      <c r="K124" t="s">
+        <v>77</v>
+      </c>
+      <c r="L124">
+        <v>5.49</v>
+      </c>
+      <c r="N124" s="6"/>
+      <c r="O124" s="5"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B125" s="6">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="C125" s="5">
+        <f t="shared" si="8"/>
+        <v>11.409999999999998</v>
+      </c>
+      <c r="D125" s="5">
+        <f t="shared" si="9"/>
+        <v>22.39</v>
+      </c>
+      <c r="E125" s="5">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F125">
+        <v>24</v>
+      </c>
+      <c r="G125" s="8">
+        <v>22</v>
+      </c>
       <c r="H125" s="8"/>
-    </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I125" t="s">
+        <v>88</v>
+      </c>
+      <c r="J125" t="s">
+        <v>82</v>
+      </c>
+      <c r="K125" t="s">
+        <v>77</v>
+      </c>
+      <c r="L125">
+        <v>5.49</v>
+      </c>
+      <c r="N125" s="6"/>
+      <c r="O125" s="5"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B126" s="6">
+        <v>17.48</v>
+      </c>
+      <c r="C126" s="5">
+        <f t="shared" si="8"/>
+        <v>11.99</v>
+      </c>
+      <c r="D126" s="5">
+        <f t="shared" si="9"/>
+        <v>22.97</v>
+      </c>
+      <c r="E126" s="5">
+        <v>22.97</v>
+      </c>
+      <c r="F126">
+        <v>25</v>
+      </c>
+      <c r="G126" s="8">
+        <v>25</v>
+      </c>
       <c r="H126" s="8"/>
-    </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I126" t="s">
+        <v>88</v>
+      </c>
+      <c r="J126" t="s">
+        <v>82</v>
+      </c>
+      <c r="K126" t="s">
+        <v>77</v>
+      </c>
+      <c r="L126">
+        <v>5.49</v>
+      </c>
+      <c r="N126" s="6"/>
+      <c r="O126" s="5"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="H128" s="8"/>
     </row>
     <row r="129" spans="8:8" x14ac:dyDescent="0.55000000000000004">
@@ -7259,8 +8281,8 @@
       <c r="H357" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N28:O52">
-    <sortCondition ref="O28:O52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N102:O126">
+    <sortCondition ref="O102:O126"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7273,7 +8295,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="17.20703125" bestFit="1" customWidth="1"/>
@@ -11420,11 +12442,11 @@
       </c>
       <c r="C101" s="5">
         <f t="shared" si="6"/>
-        <v>12.34</v>
+        <v>12.399999999999999</v>
       </c>
       <c r="D101" s="5">
         <f t="shared" si="5"/>
-        <v>22.74</v>
+        <v>22.68</v>
       </c>
       <c r="E101" s="5">
         <v>22.74</v>
@@ -11448,14 +12470,462 @@
         <v>86</v>
       </c>
       <c r="L101" s="5">
-        <v>5.2</v>
+        <v>5.14</v>
       </c>
       <c r="N101" s="6"/>
       <c r="O101" s="5"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="H102" s="8"/>
+      <c r="I102" t="s">
+        <v>88</v>
+      </c>
+      <c r="J102" t="s">
+        <v>82</v>
+      </c>
+      <c r="K102" t="s">
+        <v>86</v>
+      </c>
+      <c r="L102" s="5">
+        <v>5.14</v>
+      </c>
       <c r="N102" s="6"/>
       <c r="O102" s="5"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F103">
+        <v>2</v>
+      </c>
+      <c r="H103" s="8"/>
+      <c r="I103" t="s">
+        <v>88</v>
+      </c>
+      <c r="J103" t="s">
+        <v>82</v>
+      </c>
+      <c r="K103" t="s">
+        <v>86</v>
+      </c>
+      <c r="L103" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F104">
+        <v>3</v>
+      </c>
+      <c r="H104" s="8"/>
+      <c r="I104" t="s">
+        <v>88</v>
+      </c>
+      <c r="J104" t="s">
+        <v>82</v>
+      </c>
+      <c r="K104" t="s">
+        <v>86</v>
+      </c>
+      <c r="L104" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F105">
+        <v>4</v>
+      </c>
+      <c r="H105" s="8"/>
+      <c r="I105" t="s">
+        <v>88</v>
+      </c>
+      <c r="J105" t="s">
+        <v>82</v>
+      </c>
+      <c r="K105" t="s">
+        <v>86</v>
+      </c>
+      <c r="L105" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F106">
+        <v>5</v>
+      </c>
+      <c r="H106" s="8"/>
+      <c r="I106" t="s">
+        <v>88</v>
+      </c>
+      <c r="J106" t="s">
+        <v>82</v>
+      </c>
+      <c r="K106" t="s">
+        <v>86</v>
+      </c>
+      <c r="L106" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F107">
+        <v>6</v>
+      </c>
+      <c r="H107" s="8"/>
+      <c r="I107" t="s">
+        <v>88</v>
+      </c>
+      <c r="J107" t="s">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s">
+        <v>86</v>
+      </c>
+      <c r="L107" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F108">
+        <v>7</v>
+      </c>
+      <c r="H108" s="8"/>
+      <c r="I108" t="s">
+        <v>88</v>
+      </c>
+      <c r="J108" t="s">
+        <v>82</v>
+      </c>
+      <c r="K108" t="s">
+        <v>86</v>
+      </c>
+      <c r="L108" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F109">
+        <v>8</v>
+      </c>
+      <c r="H109" s="8"/>
+      <c r="I109" t="s">
+        <v>88</v>
+      </c>
+      <c r="J109" t="s">
+        <v>82</v>
+      </c>
+      <c r="K109" t="s">
+        <v>86</v>
+      </c>
+      <c r="L109" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F110">
+        <v>9</v>
+      </c>
+      <c r="H110" s="8"/>
+      <c r="I110" t="s">
+        <v>88</v>
+      </c>
+      <c r="J110" t="s">
+        <v>82</v>
+      </c>
+      <c r="K110" t="s">
+        <v>86</v>
+      </c>
+      <c r="L110" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F111">
+        <v>10</v>
+      </c>
+      <c r="H111" s="8"/>
+      <c r="I111" t="s">
+        <v>88</v>
+      </c>
+      <c r="J111" t="s">
+        <v>82</v>
+      </c>
+      <c r="K111" t="s">
+        <v>86</v>
+      </c>
+      <c r="L111" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F112">
+        <v>11</v>
+      </c>
+      <c r="H112" s="8"/>
+      <c r="I112" t="s">
+        <v>88</v>
+      </c>
+      <c r="J112" t="s">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s">
+        <v>86</v>
+      </c>
+      <c r="L112" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="113" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F113">
+        <v>12</v>
+      </c>
+      <c r="H113" s="8"/>
+      <c r="I113" t="s">
+        <v>88</v>
+      </c>
+      <c r="J113" t="s">
+        <v>82</v>
+      </c>
+      <c r="K113" t="s">
+        <v>86</v>
+      </c>
+      <c r="L113" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="114" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F114">
+        <v>13</v>
+      </c>
+      <c r="H114" s="8"/>
+      <c r="I114" t="s">
+        <v>88</v>
+      </c>
+      <c r="J114" t="s">
+        <v>82</v>
+      </c>
+      <c r="K114" t="s">
+        <v>86</v>
+      </c>
+      <c r="L114" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="115" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F115">
+        <v>14</v>
+      </c>
+      <c r="H115" s="8"/>
+      <c r="I115" t="s">
+        <v>88</v>
+      </c>
+      <c r="J115" t="s">
+        <v>82</v>
+      </c>
+      <c r="K115" t="s">
+        <v>86</v>
+      </c>
+      <c r="L115" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="116" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F116">
+        <v>15</v>
+      </c>
+      <c r="H116" s="8"/>
+      <c r="I116" t="s">
+        <v>88</v>
+      </c>
+      <c r="J116" t="s">
+        <v>82</v>
+      </c>
+      <c r="K116" t="s">
+        <v>86</v>
+      </c>
+      <c r="L116" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="117" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F117">
+        <v>16</v>
+      </c>
+      <c r="H117" s="8"/>
+      <c r="I117" t="s">
+        <v>88</v>
+      </c>
+      <c r="J117" t="s">
+        <v>82</v>
+      </c>
+      <c r="K117" t="s">
+        <v>86</v>
+      </c>
+      <c r="L117" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="118" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F118">
+        <v>17</v>
+      </c>
+      <c r="H118" s="8"/>
+      <c r="I118" t="s">
+        <v>88</v>
+      </c>
+      <c r="J118" t="s">
+        <v>82</v>
+      </c>
+      <c r="K118" t="s">
+        <v>86</v>
+      </c>
+      <c r="L118" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="119" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F119">
+        <v>18</v>
+      </c>
+      <c r="H119" s="8"/>
+      <c r="I119" t="s">
+        <v>88</v>
+      </c>
+      <c r="J119" t="s">
+        <v>82</v>
+      </c>
+      <c r="K119" t="s">
+        <v>86</v>
+      </c>
+      <c r="L119" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="120" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F120">
+        <v>19</v>
+      </c>
+      <c r="H120" s="8"/>
+      <c r="I120" t="s">
+        <v>88</v>
+      </c>
+      <c r="J120" t="s">
+        <v>82</v>
+      </c>
+      <c r="K120" t="s">
+        <v>86</v>
+      </c>
+      <c r="L120" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="121" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F121">
+        <v>20</v>
+      </c>
+      <c r="H121" s="8"/>
+      <c r="I121" t="s">
+        <v>88</v>
+      </c>
+      <c r="J121" t="s">
+        <v>82</v>
+      </c>
+      <c r="K121" t="s">
+        <v>86</v>
+      </c>
+      <c r="L121" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="122" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F122">
+        <v>21</v>
+      </c>
+      <c r="H122" s="8"/>
+      <c r="I122" t="s">
+        <v>88</v>
+      </c>
+      <c r="J122" t="s">
+        <v>82</v>
+      </c>
+      <c r="K122" t="s">
+        <v>86</v>
+      </c>
+      <c r="L122" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="123" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F123">
+        <v>22</v>
+      </c>
+      <c r="H123" s="8"/>
+      <c r="I123" t="s">
+        <v>88</v>
+      </c>
+      <c r="J123" t="s">
+        <v>82</v>
+      </c>
+      <c r="K123" t="s">
+        <v>86</v>
+      </c>
+      <c r="L123" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="124" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F124">
+        <v>23</v>
+      </c>
+      <c r="H124" s="8"/>
+      <c r="I124" t="s">
+        <v>88</v>
+      </c>
+      <c r="J124" t="s">
+        <v>82</v>
+      </c>
+      <c r="K124" t="s">
+        <v>86</v>
+      </c>
+      <c r="L124" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="125" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F125">
+        <v>24</v>
+      </c>
+      <c r="H125" s="8"/>
+      <c r="I125" t="s">
+        <v>88</v>
+      </c>
+      <c r="J125" t="s">
+        <v>82</v>
+      </c>
+      <c r="K125" t="s">
+        <v>86</v>
+      </c>
+      <c r="L125" s="5">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="126" spans="6:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="F126">
+        <v>25</v>
+      </c>
+      <c r="H126" s="8"/>
+      <c r="I126" t="s">
+        <v>88</v>
+      </c>
+      <c r="J126" t="s">
+        <v>82</v>
+      </c>
+      <c r="K126" t="s">
+        <v>86</v>
+      </c>
+      <c r="L126" s="5">
+        <v>5.14</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N78:O102">
